--- a/90_通用工具_全学期复用/90-C4_学生档案汇总表_v2.4_20260820.xlsx
+++ b/90_通用工具_全学期复用/90-C4_学生档案汇总表_v2.4_20260820.xlsx
@@ -322,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -478,6 +478,12 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -879,7 +885,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B80"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -1242,16 +1248,16 @@
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="54" t="inlineStr">
-        <is>
-          <t>Q：作业布置什么？书后课后题吗？我还得一本一本改吗？</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="52" customHeight="1">
-      <c r="A55" s="53" t="inlineStr">
-        <is>
-          <t>A：不要收书后课后题，42 本改不动，第三周会放弃。90-C00 已经定了：平时靠课堂上举册子抽查，不收作业。只有两类东西才打 0/2/5：每个项目最后一节的企业微信收集表（一学期大约 9 次）；加分题里最难的几道用收集表收（一学期大约 4 次）。批改只分三档：没写 0、写了跑题 2、写了切题 5，不细究对错，大约 30 分钟一批。没有收集表的那一周，计算器 E、F 列空着。课堂上点名器已经加过的，不要再当作业加一遍。</t>
+      <c r="A54" s="68" t="inlineStr">
+        <is>
+          <t>Q：作业布置什么？「项目最后一节收集表」「加分题」是什么？</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="72" customHeight="1">
+      <c r="A55" s="69" t="inlineStr">
+        <is>
+          <t>A：先把两句话拆开。它们都不是你刚做的开学点单。「加分题」= 主文档里写了「加分题」的那几个暂停点（项目一是第5题、第14题这种），学生写在记录册上，你抽 3 人举册子看，写对 5 分。不要另做企业微信。「项目最后一节收集表」= 以前设想过项目上完再发一张 3～5 题的短表。仓库里还没有现成的。你现在不必做。项目结束看点名器积分、评谁表现好就行。书后课后题不要收。没有短表的那一周，计算器作业列空着。</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1472,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -1787,7 +1793,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AF52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2064,7 +2070,7 @@
         <v/>
       </c>
       <c r="AE3" s="10">
-        <f>IF(V3="","",IF(OR(V3="不要用我的照片",V3="只给我自己看"),"★形象不可公开",IF(V3="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V3&amp;"")="","",IF(OR(TRIM(V3)="不要用我的照片",TRIM(V3)="只给我自己看"),"★形象不可公开",IF(TRIM(V3)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF3" s="8" t="n"/>
@@ -2110,7 +2116,7 @@
         <v/>
       </c>
       <c r="AE4" s="10">
-        <f>IF(V4="","",IF(OR(V4="不要用我的照片",V4="只给我自己看"),"★形象不可公开",IF(V4="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V4&amp;"")="","",IF(OR(TRIM(V4)="不要用我的照片",TRIM(V4)="只给我自己看"),"★形象不可公开",IF(TRIM(V4)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF4" s="11" t="n"/>
@@ -2156,7 +2162,7 @@
         <v/>
       </c>
       <c r="AE5" s="10">
-        <f>IF(V5="","",IF(OR(V5="不要用我的照片",V5="只给我自己看"),"★形象不可公开",IF(V5="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V5&amp;"")="","",IF(OR(TRIM(V5)="不要用我的照片",TRIM(V5)="只给我自己看"),"★形象不可公开",IF(TRIM(V5)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF5" s="8" t="n"/>
@@ -2202,7 +2208,7 @@
         <v/>
       </c>
       <c r="AE6" s="10">
-        <f>IF(V6="","",IF(OR(V6="不要用我的照片",V6="只给我自己看"),"★形象不可公开",IF(V6="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V6&amp;"")="","",IF(OR(TRIM(V6)="不要用我的照片",TRIM(V6)="只给我自己看"),"★形象不可公开",IF(TRIM(V6)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF6" s="11" t="n"/>
@@ -2248,7 +2254,7 @@
         <v/>
       </c>
       <c r="AE7" s="10">
-        <f>IF(V7="","",IF(OR(V7="不要用我的照片",V7="只给我自己看"),"★形象不可公开",IF(V7="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V7&amp;"")="","",IF(OR(TRIM(V7)="不要用我的照片",TRIM(V7)="只给我自己看"),"★形象不可公开",IF(TRIM(V7)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF7" s="8" t="n"/>
@@ -2294,7 +2300,7 @@
         <v/>
       </c>
       <c r="AE8" s="10">
-        <f>IF(V8="","",IF(OR(V8="不要用我的照片",V8="只给我自己看"),"★形象不可公开",IF(V8="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V8&amp;"")="","",IF(OR(TRIM(V8)="不要用我的照片",TRIM(V8)="只给我自己看"),"★形象不可公开",IF(TRIM(V8)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF8" s="11" t="n"/>
@@ -2340,7 +2346,7 @@
         <v/>
       </c>
       <c r="AE9" s="10">
-        <f>IF(V9="","",IF(OR(V9="不要用我的照片",V9="只给我自己看"),"★形象不可公开",IF(V9="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V9&amp;"")="","",IF(OR(TRIM(V9)="不要用我的照片",TRIM(V9)="只给我自己看"),"★形象不可公开",IF(TRIM(V9)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF9" s="8" t="n"/>
@@ -2386,7 +2392,7 @@
         <v/>
       </c>
       <c r="AE10" s="10">
-        <f>IF(V10="","",IF(OR(V10="不要用我的照片",V10="只给我自己看"),"★形象不可公开",IF(V10="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V10&amp;"")="","",IF(OR(TRIM(V10)="不要用我的照片",TRIM(V10)="只给我自己看"),"★形象不可公开",IF(TRIM(V10)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF10" s="11" t="n"/>
@@ -2432,7 +2438,7 @@
         <v/>
       </c>
       <c r="AE11" s="10">
-        <f>IF(V11="","",IF(OR(V11="不要用我的照片",V11="只给我自己看"),"★形象不可公开",IF(V11="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V11&amp;"")="","",IF(OR(TRIM(V11)="不要用我的照片",TRIM(V11)="只给我自己看"),"★形象不可公开",IF(TRIM(V11)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF11" s="8" t="n"/>
@@ -2478,7 +2484,7 @@
         <v/>
       </c>
       <c r="AE12" s="10">
-        <f>IF(V12="","",IF(OR(V12="不要用我的照片",V12="只给我自己看"),"★形象不可公开",IF(V12="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V12&amp;"")="","",IF(OR(TRIM(V12)="不要用我的照片",TRIM(V12)="只给我自己看"),"★形象不可公开",IF(TRIM(V12)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF12" s="11" t="n"/>
@@ -2524,7 +2530,7 @@
         <v/>
       </c>
       <c r="AE13" s="10">
-        <f>IF(V13="","",IF(OR(V13="不要用我的照片",V13="只给我自己看"),"★形象不可公开",IF(V13="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V13&amp;"")="","",IF(OR(TRIM(V13)="不要用我的照片",TRIM(V13)="只给我自己看"),"★形象不可公开",IF(TRIM(V13)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF13" s="8" t="n"/>
@@ -2570,7 +2576,7 @@
         <v/>
       </c>
       <c r="AE14" s="10">
-        <f>IF(V14="","",IF(OR(V14="不要用我的照片",V14="只给我自己看"),"★形象不可公开",IF(V14="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V14&amp;"")="","",IF(OR(TRIM(V14)="不要用我的照片",TRIM(V14)="只给我自己看"),"★形象不可公开",IF(TRIM(V14)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF14" s="11" t="n"/>
@@ -2616,7 +2622,7 @@
         <v/>
       </c>
       <c r="AE15" s="10">
-        <f>IF(V15="","",IF(OR(V15="不要用我的照片",V15="只给我自己看"),"★形象不可公开",IF(V15="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V15&amp;"")="","",IF(OR(TRIM(V15)="不要用我的照片",TRIM(V15)="只给我自己看"),"★形象不可公开",IF(TRIM(V15)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF15" s="8" t="n"/>
@@ -2662,7 +2668,7 @@
         <v/>
       </c>
       <c r="AE16" s="10">
-        <f>IF(V16="","",IF(OR(V16="不要用我的照片",V16="只给我自己看"),"★形象不可公开",IF(V16="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V16&amp;"")="","",IF(OR(TRIM(V16)="不要用我的照片",TRIM(V16)="只给我自己看"),"★形象不可公开",IF(TRIM(V16)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF16" s="11" t="n"/>
@@ -2708,7 +2714,7 @@
         <v/>
       </c>
       <c r="AE17" s="10">
-        <f>IF(V17="","",IF(OR(V17="不要用我的照片",V17="只给我自己看"),"★形象不可公开",IF(V17="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V17&amp;"")="","",IF(OR(TRIM(V17)="不要用我的照片",TRIM(V17)="只给我自己看"),"★形象不可公开",IF(TRIM(V17)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF17" s="8" t="n"/>
@@ -2754,7 +2760,7 @@
         <v/>
       </c>
       <c r="AE18" s="10">
-        <f>IF(V18="","",IF(OR(V18="不要用我的照片",V18="只给我自己看"),"★形象不可公开",IF(V18="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V18&amp;"")="","",IF(OR(TRIM(V18)="不要用我的照片",TRIM(V18)="只给我自己看"),"★形象不可公开",IF(TRIM(V18)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF18" s="11" t="n"/>
@@ -2800,7 +2806,7 @@
         <v/>
       </c>
       <c r="AE19" s="10">
-        <f>IF(V19="","",IF(OR(V19="不要用我的照片",V19="只给我自己看"),"★形象不可公开",IF(V19="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V19&amp;"")="","",IF(OR(TRIM(V19)="不要用我的照片",TRIM(V19)="只给我自己看"),"★形象不可公开",IF(TRIM(V19)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF19" s="8" t="n"/>
@@ -2846,7 +2852,7 @@
         <v/>
       </c>
       <c r="AE20" s="10">
-        <f>IF(V20="","",IF(OR(V20="不要用我的照片",V20="只给我自己看"),"★形象不可公开",IF(V20="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V20&amp;"")="","",IF(OR(TRIM(V20)="不要用我的照片",TRIM(V20)="只给我自己看"),"★形象不可公开",IF(TRIM(V20)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF20" s="11" t="n"/>
@@ -2892,7 +2898,7 @@
         <v/>
       </c>
       <c r="AE21" s="10">
-        <f>IF(V21="","",IF(OR(V21="不要用我的照片",V21="只给我自己看"),"★形象不可公开",IF(V21="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V21&amp;"")="","",IF(OR(TRIM(V21)="不要用我的照片",TRIM(V21)="只给我自己看"),"★形象不可公开",IF(TRIM(V21)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF21" s="8" t="n"/>
@@ -2938,7 +2944,7 @@
         <v/>
       </c>
       <c r="AE22" s="10">
-        <f>IF(V22="","",IF(OR(V22="不要用我的照片",V22="只给我自己看"),"★形象不可公开",IF(V22="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V22&amp;"")="","",IF(OR(TRIM(V22)="不要用我的照片",TRIM(V22)="只给我自己看"),"★形象不可公开",IF(TRIM(V22)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF22" s="11" t="n"/>
@@ -2984,7 +2990,7 @@
         <v/>
       </c>
       <c r="AE23" s="10">
-        <f>IF(V23="","",IF(OR(V23="不要用我的照片",V23="只给我自己看"),"★形象不可公开",IF(V23="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V23&amp;"")="","",IF(OR(TRIM(V23)="不要用我的照片",TRIM(V23)="只给我自己看"),"★形象不可公开",IF(TRIM(V23)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF23" s="8" t="n"/>
@@ -3030,7 +3036,7 @@
         <v/>
       </c>
       <c r="AE24" s="10">
-        <f>IF(V24="","",IF(OR(V24="不要用我的照片",V24="只给我自己看"),"★形象不可公开",IF(V24="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V24&amp;"")="","",IF(OR(TRIM(V24)="不要用我的照片",TRIM(V24)="只给我自己看"),"★形象不可公开",IF(TRIM(V24)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF24" s="11" t="n"/>
@@ -3076,7 +3082,7 @@
         <v/>
       </c>
       <c r="AE25" s="10">
-        <f>IF(V25="","",IF(OR(V25="不要用我的照片",V25="只给我自己看"),"★形象不可公开",IF(V25="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V25&amp;"")="","",IF(OR(TRIM(V25)="不要用我的照片",TRIM(V25)="只给我自己看"),"★形象不可公开",IF(TRIM(V25)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF25" s="8" t="n"/>
@@ -3122,7 +3128,7 @@
         <v/>
       </c>
       <c r="AE26" s="10">
-        <f>IF(V26="","",IF(OR(V26="不要用我的照片",V26="只给我自己看"),"★形象不可公开",IF(V26="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V26&amp;"")="","",IF(OR(TRIM(V26)="不要用我的照片",TRIM(V26)="只给我自己看"),"★形象不可公开",IF(TRIM(V26)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF26" s="11" t="n"/>
@@ -3168,7 +3174,7 @@
         <v/>
       </c>
       <c r="AE27" s="10">
-        <f>IF(V27="","",IF(OR(V27="不要用我的照片",V27="只给我自己看"),"★形象不可公开",IF(V27="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V27&amp;"")="","",IF(OR(TRIM(V27)="不要用我的照片",TRIM(V27)="只给我自己看"),"★形象不可公开",IF(TRIM(V27)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF27" s="8" t="n"/>
@@ -3214,7 +3220,7 @@
         <v/>
       </c>
       <c r="AE28" s="10">
-        <f>IF(V28="","",IF(OR(V28="不要用我的照片",V28="只给我自己看"),"★形象不可公开",IF(V28="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V28&amp;"")="","",IF(OR(TRIM(V28)="不要用我的照片",TRIM(V28)="只给我自己看"),"★形象不可公开",IF(TRIM(V28)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF28" s="11" t="n"/>
@@ -3260,7 +3266,7 @@
         <v/>
       </c>
       <c r="AE29" s="10">
-        <f>IF(V29="","",IF(OR(V29="不要用我的照片",V29="只给我自己看"),"★形象不可公开",IF(V29="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V29&amp;"")="","",IF(OR(TRIM(V29)="不要用我的照片",TRIM(V29)="只给我自己看"),"★形象不可公开",IF(TRIM(V29)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF29" s="8" t="n"/>
@@ -3306,7 +3312,7 @@
         <v/>
       </c>
       <c r="AE30" s="10">
-        <f>IF(V30="","",IF(OR(V30="不要用我的照片",V30="只给我自己看"),"★形象不可公开",IF(V30="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V30&amp;"")="","",IF(OR(TRIM(V30)="不要用我的照片",TRIM(V30)="只给我自己看"),"★形象不可公开",IF(TRIM(V30)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF30" s="11" t="n"/>
@@ -3352,7 +3358,7 @@
         <v/>
       </c>
       <c r="AE31" s="10">
-        <f>IF(V31="","",IF(OR(V31="不要用我的照片",V31="只给我自己看"),"★形象不可公开",IF(V31="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V31&amp;"")="","",IF(OR(TRIM(V31)="不要用我的照片",TRIM(V31)="只给我自己看"),"★形象不可公开",IF(TRIM(V31)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF31" s="8" t="n"/>
@@ -3398,7 +3404,7 @@
         <v/>
       </c>
       <c r="AE32" s="10">
-        <f>IF(V32="","",IF(OR(V32="不要用我的照片",V32="只给我自己看"),"★形象不可公开",IF(V32="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V32&amp;"")="","",IF(OR(TRIM(V32)="不要用我的照片",TRIM(V32)="只给我自己看"),"★形象不可公开",IF(TRIM(V32)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF32" s="11" t="n"/>
@@ -3444,7 +3450,7 @@
         <v/>
       </c>
       <c r="AE33" s="10">
-        <f>IF(V33="","",IF(OR(V33="不要用我的照片",V33="只给我自己看"),"★形象不可公开",IF(V33="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V33&amp;"")="","",IF(OR(TRIM(V33)="不要用我的照片",TRIM(V33)="只给我自己看"),"★形象不可公开",IF(TRIM(V33)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF33" s="8" t="n"/>
@@ -3490,7 +3496,7 @@
         <v/>
       </c>
       <c r="AE34" s="10">
-        <f>IF(V34="","",IF(OR(V34="不要用我的照片",V34="只给我自己看"),"★形象不可公开",IF(V34="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V34&amp;"")="","",IF(OR(TRIM(V34)="不要用我的照片",TRIM(V34)="只给我自己看"),"★形象不可公开",IF(TRIM(V34)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF34" s="11" t="n"/>
@@ -3536,7 +3542,7 @@
         <v/>
       </c>
       <c r="AE35" s="10">
-        <f>IF(V35="","",IF(OR(V35="不要用我的照片",V35="只给我自己看"),"★形象不可公开",IF(V35="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V35&amp;"")="","",IF(OR(TRIM(V35)="不要用我的照片",TRIM(V35)="只给我自己看"),"★形象不可公开",IF(TRIM(V35)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF35" s="8" t="n"/>
@@ -3582,7 +3588,7 @@
         <v/>
       </c>
       <c r="AE36" s="10">
-        <f>IF(V36="","",IF(OR(V36="不要用我的照片",V36="只给我自己看"),"★形象不可公开",IF(V36="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V36&amp;"")="","",IF(OR(TRIM(V36)="不要用我的照片",TRIM(V36)="只给我自己看"),"★形象不可公开",IF(TRIM(V36)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF36" s="11" t="n"/>
@@ -3628,7 +3634,7 @@
         <v/>
       </c>
       <c r="AE37" s="10">
-        <f>IF(V37="","",IF(OR(V37="不要用我的照片",V37="只给我自己看"),"★形象不可公开",IF(V37="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V37&amp;"")="","",IF(OR(TRIM(V37)="不要用我的照片",TRIM(V37)="只给我自己看"),"★形象不可公开",IF(TRIM(V37)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF37" s="8" t="n"/>
@@ -3674,7 +3680,7 @@
         <v/>
       </c>
       <c r="AE38" s="10">
-        <f>IF(V38="","",IF(OR(V38="不要用我的照片",V38="只给我自己看"),"★形象不可公开",IF(V38="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V38&amp;"")="","",IF(OR(TRIM(V38)="不要用我的照片",TRIM(V38)="只给我自己看"),"★形象不可公开",IF(TRIM(V38)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF38" s="11" t="n"/>
@@ -3720,7 +3726,7 @@
         <v/>
       </c>
       <c r="AE39" s="10">
-        <f>IF(V39="","",IF(OR(V39="不要用我的照片",V39="只给我自己看"),"★形象不可公开",IF(V39="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V39&amp;"")="","",IF(OR(TRIM(V39)="不要用我的照片",TRIM(V39)="只给我自己看"),"★形象不可公开",IF(TRIM(V39)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF39" s="8" t="n"/>
@@ -3766,7 +3772,7 @@
         <v/>
       </c>
       <c r="AE40" s="10">
-        <f>IF(V40="","",IF(OR(V40="不要用我的照片",V40="只给我自己看"),"★形象不可公开",IF(V40="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V40&amp;"")="","",IF(OR(TRIM(V40)="不要用我的照片",TRIM(V40)="只给我自己看"),"★形象不可公开",IF(TRIM(V40)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF40" s="11" t="n"/>
@@ -3812,7 +3818,7 @@
         <v/>
       </c>
       <c r="AE41" s="10">
-        <f>IF(V41="","",IF(OR(V41="不要用我的照片",V41="只给我自己看"),"★形象不可公开",IF(V41="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V41&amp;"")="","",IF(OR(TRIM(V41)="不要用我的照片",TRIM(V41)="只给我自己看"),"★形象不可公开",IF(TRIM(V41)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF41" s="8" t="n"/>
@@ -3858,7 +3864,7 @@
         <v/>
       </c>
       <c r="AE42" s="10">
-        <f>IF(V42="","",IF(OR(V42="不要用我的照片",V42="只给我自己看"),"★形象不可公开",IF(V42="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V42&amp;"")="","",IF(OR(TRIM(V42)="不要用我的照片",TRIM(V42)="只给我自己看"),"★形象不可公开",IF(TRIM(V42)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF42" s="11" t="n"/>
@@ -3904,7 +3910,7 @@
         <v/>
       </c>
       <c r="AE43" s="10">
-        <f>IF(V43="","",IF(OR(V43="不要用我的照片",V43="只给我自己看"),"★形象不可公开",IF(V43="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V43&amp;"")="","",IF(OR(TRIM(V43)="不要用我的照片",TRIM(V43)="只给我自己看"),"★形象不可公开",IF(TRIM(V43)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF43" s="8" t="n"/>
@@ -3950,7 +3956,7 @@
         <v/>
       </c>
       <c r="AE44" s="10">
-        <f>IF(V44="","",IF(OR(V44="不要用我的照片",V44="只给我自己看"),"★形象不可公开",IF(V44="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V44&amp;"")="","",IF(OR(TRIM(V44)="不要用我的照片",TRIM(V44)="只给我自己看"),"★形象不可公开",IF(TRIM(V44)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF44" s="11" t="n"/>
@@ -3996,7 +4002,7 @@
         <v/>
       </c>
       <c r="AE45" s="10">
-        <f>IF(V45="","",IF(OR(V45="不要用我的照片",V45="只给我自己看"),"★形象不可公开",IF(V45="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V45&amp;"")="","",IF(OR(TRIM(V45)="不要用我的照片",TRIM(V45)="只给我自己看"),"★形象不可公开",IF(TRIM(V45)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF45" s="8" t="n"/>
@@ -4042,7 +4048,7 @@
         <v/>
       </c>
       <c r="AE46" s="10">
-        <f>IF(V46="","",IF(OR(V46="不要用我的照片",V46="只给我自己看"),"★形象不可公开",IF(V46="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V46&amp;"")="","",IF(OR(TRIM(V46)="不要用我的照片",TRIM(V46)="只给我自己看"),"★形象不可公开",IF(TRIM(V46)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF46" s="11" t="n"/>
@@ -4088,7 +4094,7 @@
         <v/>
       </c>
       <c r="AE47" s="10">
-        <f>IF(V47="","",IF(OR(V47="不要用我的照片",V47="只给我自己看"),"★形象不可公开",IF(V47="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V47&amp;"")="","",IF(OR(TRIM(V47)="不要用我的照片",TRIM(V47)="只给我自己看"),"★形象不可公开",IF(TRIM(V47)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF47" s="8" t="n"/>
@@ -4134,7 +4140,7 @@
         <v/>
       </c>
       <c r="AE48" s="10">
-        <f>IF(V48="","",IF(OR(V48="不要用我的照片",V48="只给我自己看"),"★形象不可公开",IF(V48="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V48&amp;"")="","",IF(OR(TRIM(V48)="不要用我的照片",TRIM(V48)="只给我自己看"),"★形象不可公开",IF(TRIM(V48)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF48" s="11" t="n"/>
@@ -4180,7 +4186,7 @@
         <v/>
       </c>
       <c r="AE49" s="10">
-        <f>IF(V49="","",IF(OR(V49="不要用我的照片",V49="只给我自己看"),"★形象不可公开",IF(V49="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V49&amp;"")="","",IF(OR(TRIM(V49)="不要用我的照片",TRIM(V49)="只给我自己看"),"★形象不可公开",IF(TRIM(V49)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF49" s="8" t="n"/>
@@ -4226,7 +4232,7 @@
         <v/>
       </c>
       <c r="AE50" s="10">
-        <f>IF(V50="","",IF(OR(V50="不要用我的照片",V50="只给我自己看"),"★形象不可公开",IF(V50="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V50&amp;"")="","",IF(OR(TRIM(V50)="不要用我的照片",TRIM(V50)="只给我自己看"),"★形象不可公开",IF(TRIM(V50)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF50" s="11" t="n"/>
@@ -4272,7 +4278,7 @@
         <v/>
       </c>
       <c r="AE51" s="10">
-        <f>IF(V51="","",IF(OR(V51="不要用我的照片",V51="只给我自己看"),"★形象不可公开",IF(V51="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V51&amp;"")="","",IF(OR(TRIM(V51)="不要用我的照片",TRIM(V51)="只给我自己看"),"★形象不可公开",IF(TRIM(V51)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF51" s="8" t="n"/>
@@ -4318,7 +4324,7 @@
         <v/>
       </c>
       <c r="AE52" s="10">
-        <f>IF(V52="","",IF(OR(V52="不要用我的照片",V52="只给我自己看"),"★形象不可公开",IF(V52="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(TRIM(V52&amp;"")="","",IF(OR(TRIM(V52)="不要用我的照片",TRIM(V52)="只给我自己看"),"★形象不可公开",IF(TRIM(V52)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF52" s="11" t="n"/>
@@ -4365,7 +4371,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -6363,7 +6369,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U131"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -9507,7 +9513,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -10845,7 +10851,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -11911,7 +11917,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -13134,7 +13140,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M80"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -13257,7 +13263,7 @@
         <v/>
       </c>
       <c r="F3" s="17">
-        <f>IF(B3="","",IF(E3="还不错","种子-数学",IF(D3="完全没有","零基础",IF(E3="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B3="","",IF(TRIM(E3)="还不错","种子-数学",IF(TRIM(D3)="完全没有","零基础",IF(TRIM(E3)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G3" s="22" t="n"/>
@@ -13302,7 +13308,7 @@
         <v/>
       </c>
       <c r="F4" s="17">
-        <f>IF(B4="","",IF(E4="还不错","种子-数学",IF(D4="完全没有","零基础",IF(E4="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B4="","",IF(TRIM(E4)="还不错","种子-数学",IF(TRIM(D4)="完全没有","零基础",IF(TRIM(E4)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G4" s="22" t="n"/>
@@ -13347,7 +13353,7 @@
         <v/>
       </c>
       <c r="F5" s="17">
-        <f>IF(B5="","",IF(E5="还不错","种子-数学",IF(D5="完全没有","零基础",IF(E5="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B5="","",IF(TRIM(E5)="还不错","种子-数学",IF(TRIM(D5)="完全没有","零基础",IF(TRIM(E5)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G5" s="22" t="n"/>
@@ -13392,7 +13398,7 @@
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>IF(B6="","",IF(E6="还不错","种子-数学",IF(D6="完全没有","零基础",IF(E6="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B6="","",IF(TRIM(E6)="还不错","种子-数学",IF(TRIM(D6)="完全没有","零基础",IF(TRIM(E6)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G6" s="22" t="n"/>
@@ -13437,7 +13443,7 @@
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>IF(B7="","",IF(E7="还不错","种子-数学",IF(D7="完全没有","零基础",IF(E7="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B7="","",IF(TRIM(E7)="还不错","种子-数学",IF(TRIM(D7)="完全没有","零基础",IF(TRIM(E7)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G7" s="22" t="n"/>
@@ -13482,7 +13488,7 @@
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>IF(B8="","",IF(E8="还不错","种子-数学",IF(D8="完全没有","零基础",IF(E8="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B8="","",IF(TRIM(E8)="还不错","种子-数学",IF(TRIM(D8)="完全没有","零基础",IF(TRIM(E8)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G8" s="22" t="n"/>
@@ -13527,7 +13533,7 @@
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>IF(B9="","",IF(E9="还不错","种子-数学",IF(D9="完全没有","零基础",IF(E9="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B9="","",IF(TRIM(E9)="还不错","种子-数学",IF(TRIM(D9)="完全没有","零基础",IF(TRIM(E9)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G9" s="22" t="n"/>
@@ -13555,7 +13561,7 @@
         <v/>
       </c>
       <c r="F10" s="17">
-        <f>IF(B10="","",IF(E10="还不错","种子-数学",IF(D10="完全没有","零基础",IF(E10="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B10="","",IF(TRIM(E10)="还不错","种子-数学",IF(TRIM(D10)="完全没有","零基础",IF(TRIM(E10)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G10" s="22" t="n"/>
@@ -13588,7 +13594,7 @@
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>IF(B11="","",IF(E11="还不错","种子-数学",IF(D11="完全没有","零基础",IF(E11="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B11="","",IF(TRIM(E11)="还不错","种子-数学",IF(TRIM(D11)="完全没有","零基础",IF(TRIM(E11)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G11" s="22" t="n"/>
@@ -13616,7 +13622,7 @@
         <v/>
       </c>
       <c r="F12" s="17">
-        <f>IF(B12="","",IF(E12="还不错","种子-数学",IF(D12="完全没有","零基础",IF(E12="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B12="","",IF(TRIM(E12)="还不错","种子-数学",IF(TRIM(D12)="完全没有","零基础",IF(TRIM(E12)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G12" s="22" t="n"/>
@@ -13644,7 +13650,7 @@
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>IF(B13="","",IF(E13="还不错","种子-数学",IF(D13="完全没有","零基础",IF(E13="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B13="","",IF(TRIM(E13)="还不错","种子-数学",IF(TRIM(D13)="完全没有","零基础",IF(TRIM(E13)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G13" s="22" t="n"/>
@@ -13672,7 +13678,7 @@
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>IF(B14="","",IF(E14="还不错","种子-数学",IF(D14="完全没有","零基础",IF(E14="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B14="","",IF(TRIM(E14)="还不错","种子-数学",IF(TRIM(D14)="完全没有","零基础",IF(TRIM(E14)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G14" s="22" t="n"/>
@@ -13700,7 +13706,7 @@
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>IF(B15="","",IF(E15="还不错","种子-数学",IF(D15="完全没有","零基础",IF(E15="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B15="","",IF(TRIM(E15)="还不错","种子-数学",IF(TRIM(D15)="完全没有","零基础",IF(TRIM(E15)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G15" s="22" t="n"/>
@@ -13728,7 +13734,7 @@
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>IF(B16="","",IF(E16="还不错","种子-数学",IF(D16="完全没有","零基础",IF(E16="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B16="","",IF(TRIM(E16)="还不错","种子-数学",IF(TRIM(D16)="完全没有","零基础",IF(TRIM(E16)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G16" s="22" t="n"/>
@@ -13756,7 +13762,7 @@
         <v/>
       </c>
       <c r="F17" s="17">
-        <f>IF(B17="","",IF(E17="还不错","种子-数学",IF(D17="完全没有","零基础",IF(E17="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B17="","",IF(TRIM(E17)="还不错","种子-数学",IF(TRIM(D17)="完全没有","零基础",IF(TRIM(E17)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G17" s="22" t="n"/>
@@ -13784,7 +13790,7 @@
         <v/>
       </c>
       <c r="F18" s="17">
-        <f>IF(B18="","",IF(E18="还不错","种子-数学",IF(D18="完全没有","零基础",IF(E18="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B18="","",IF(TRIM(E18)="还不错","种子-数学",IF(TRIM(D18)="完全没有","零基础",IF(TRIM(E18)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G18" s="22" t="n"/>
@@ -13812,7 +13818,7 @@
         <v/>
       </c>
       <c r="F19" s="17">
-        <f>IF(B19="","",IF(E19="还不错","种子-数学",IF(D19="完全没有","零基础",IF(E19="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B19="","",IF(TRIM(E19)="还不错","种子-数学",IF(TRIM(D19)="完全没有","零基础",IF(TRIM(E19)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G19" s="22" t="n"/>
@@ -13840,7 +13846,7 @@
         <v/>
       </c>
       <c r="F20" s="17">
-        <f>IF(B20="","",IF(E20="还不错","种子-数学",IF(D20="完全没有","零基础",IF(E20="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B20="","",IF(TRIM(E20)="还不错","种子-数学",IF(TRIM(D20)="完全没有","零基础",IF(TRIM(E20)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G20" s="22" t="n"/>
@@ -13868,7 +13874,7 @@
         <v/>
       </c>
       <c r="F21" s="17">
-        <f>IF(B21="","",IF(E21="还不错","种子-数学",IF(D21="完全没有","零基础",IF(E21="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B21="","",IF(TRIM(E21)="还不错","种子-数学",IF(TRIM(D21)="完全没有","零基础",IF(TRIM(E21)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G21" s="22" t="n"/>
@@ -13896,7 +13902,7 @@
         <v/>
       </c>
       <c r="F22" s="17">
-        <f>IF(B22="","",IF(E22="还不错","种子-数学",IF(D22="完全没有","零基础",IF(E22="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B22="","",IF(TRIM(E22)="还不错","种子-数学",IF(TRIM(D22)="完全没有","零基础",IF(TRIM(E22)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G22" s="22" t="n"/>
@@ -13924,7 +13930,7 @@
         <v/>
       </c>
       <c r="F23" s="17">
-        <f>IF(B23="","",IF(E23="还不错","种子-数学",IF(D23="完全没有","零基础",IF(E23="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B23="","",IF(TRIM(E23)="还不错","种子-数学",IF(TRIM(D23)="完全没有","零基础",IF(TRIM(E23)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G23" s="22" t="n"/>
@@ -13952,7 +13958,7 @@
         <v/>
       </c>
       <c r="F24" s="17">
-        <f>IF(B24="","",IF(E24="还不错","种子-数学",IF(D24="完全没有","零基础",IF(E24="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B24="","",IF(TRIM(E24)="还不错","种子-数学",IF(TRIM(D24)="完全没有","零基础",IF(TRIM(E24)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G24" s="22" t="n"/>
@@ -13980,7 +13986,7 @@
         <v/>
       </c>
       <c r="F25" s="17">
-        <f>IF(B25="","",IF(E25="还不错","种子-数学",IF(D25="完全没有","零基础",IF(E25="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B25="","",IF(TRIM(E25)="还不错","种子-数学",IF(TRIM(D25)="完全没有","零基础",IF(TRIM(E25)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G25" s="22" t="n"/>
@@ -14008,7 +14014,7 @@
         <v/>
       </c>
       <c r="F26" s="17">
-        <f>IF(B26="","",IF(E26="还不错","种子-数学",IF(D26="完全没有","零基础",IF(E26="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B26="","",IF(TRIM(E26)="还不错","种子-数学",IF(TRIM(D26)="完全没有","零基础",IF(TRIM(E26)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G26" s="22" t="n"/>
@@ -14036,7 +14042,7 @@
         <v/>
       </c>
       <c r="F27" s="17">
-        <f>IF(B27="","",IF(E27="还不错","种子-数学",IF(D27="完全没有","零基础",IF(E27="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B27="","",IF(TRIM(E27)="还不错","种子-数学",IF(TRIM(D27)="完全没有","零基础",IF(TRIM(E27)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G27" s="22" t="n"/>
@@ -14064,7 +14070,7 @@
         <v/>
       </c>
       <c r="F28" s="17">
-        <f>IF(B28="","",IF(E28="还不错","种子-数学",IF(D28="完全没有","零基础",IF(E28="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B28="","",IF(TRIM(E28)="还不错","种子-数学",IF(TRIM(D28)="完全没有","零基础",IF(TRIM(E28)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G28" s="22" t="n"/>
@@ -14092,7 +14098,7 @@
         <v/>
       </c>
       <c r="F29" s="17">
-        <f>IF(B29="","",IF(E29="还不错","种子-数学",IF(D29="完全没有","零基础",IF(E29="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B29="","",IF(TRIM(E29)="还不错","种子-数学",IF(TRIM(D29)="完全没有","零基础",IF(TRIM(E29)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G29" s="22" t="n"/>
@@ -14120,7 +14126,7 @@
         <v/>
       </c>
       <c r="F30" s="17">
-        <f>IF(B30="","",IF(E30="还不错","种子-数学",IF(D30="完全没有","零基础",IF(E30="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B30="","",IF(TRIM(E30)="还不错","种子-数学",IF(TRIM(D30)="完全没有","零基础",IF(TRIM(E30)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G30" s="22" t="n"/>
@@ -14148,7 +14154,7 @@
         <v/>
       </c>
       <c r="F31" s="17">
-        <f>IF(B31="","",IF(E31="还不错","种子-数学",IF(D31="完全没有","零基础",IF(E31="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B31="","",IF(TRIM(E31)="还不错","种子-数学",IF(TRIM(D31)="完全没有","零基础",IF(TRIM(E31)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G31" s="22" t="n"/>
@@ -14176,7 +14182,7 @@
         <v/>
       </c>
       <c r="F32" s="17">
-        <f>IF(B32="","",IF(E32="还不错","种子-数学",IF(D32="完全没有","零基础",IF(E32="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B32="","",IF(TRIM(E32)="还不错","种子-数学",IF(TRIM(D32)="完全没有","零基础",IF(TRIM(E32)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G32" s="22" t="n"/>
@@ -14204,7 +14210,7 @@
         <v/>
       </c>
       <c r="F33" s="17">
-        <f>IF(B33="","",IF(E33="还不错","种子-数学",IF(D33="完全没有","零基础",IF(E33="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B33="","",IF(TRIM(E33)="还不错","种子-数学",IF(TRIM(D33)="完全没有","零基础",IF(TRIM(E33)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G33" s="22" t="n"/>
@@ -14232,7 +14238,7 @@
         <v/>
       </c>
       <c r="F34" s="17">
-        <f>IF(B34="","",IF(E34="还不错","种子-数学",IF(D34="完全没有","零基础",IF(E34="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B34="","",IF(TRIM(E34)="还不错","种子-数学",IF(TRIM(D34)="完全没有","零基础",IF(TRIM(E34)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G34" s="22" t="n"/>
@@ -14260,7 +14266,7 @@
         <v/>
       </c>
       <c r="F35" s="17">
-        <f>IF(B35="","",IF(E35="还不错","种子-数学",IF(D35="完全没有","零基础",IF(E35="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B35="","",IF(TRIM(E35)="还不错","种子-数学",IF(TRIM(D35)="完全没有","零基础",IF(TRIM(E35)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G35" s="22" t="n"/>
@@ -14288,7 +14294,7 @@
         <v/>
       </c>
       <c r="F36" s="17">
-        <f>IF(B36="","",IF(E36="还不错","种子-数学",IF(D36="完全没有","零基础",IF(E36="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B36="","",IF(TRIM(E36)="还不错","种子-数学",IF(TRIM(D36)="完全没有","零基础",IF(TRIM(E36)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G36" s="22" t="n"/>
@@ -14316,7 +14322,7 @@
         <v/>
       </c>
       <c r="F37" s="17">
-        <f>IF(B37="","",IF(E37="还不错","种子-数学",IF(D37="完全没有","零基础",IF(E37="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B37="","",IF(TRIM(E37)="还不错","种子-数学",IF(TRIM(D37)="完全没有","零基础",IF(TRIM(E37)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G37" s="22" t="n"/>
@@ -14344,7 +14350,7 @@
         <v/>
       </c>
       <c r="F38" s="17">
-        <f>IF(B38="","",IF(E38="还不错","种子-数学",IF(D38="完全没有","零基础",IF(E38="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B38="","",IF(TRIM(E38)="还不错","种子-数学",IF(TRIM(D38)="完全没有","零基础",IF(TRIM(E38)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G38" s="22" t="n"/>
@@ -14372,7 +14378,7 @@
         <v/>
       </c>
       <c r="F39" s="17">
-        <f>IF(B39="","",IF(E39="还不错","种子-数学",IF(D39="完全没有","零基础",IF(E39="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B39="","",IF(TRIM(E39)="还不错","种子-数学",IF(TRIM(D39)="完全没有","零基础",IF(TRIM(E39)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G39" s="22" t="n"/>
@@ -14400,7 +14406,7 @@
         <v/>
       </c>
       <c r="F40" s="17">
-        <f>IF(B40="","",IF(E40="还不错","种子-数学",IF(D40="完全没有","零基础",IF(E40="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B40="","",IF(TRIM(E40)="还不错","种子-数学",IF(TRIM(D40)="完全没有","零基础",IF(TRIM(E40)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G40" s="22" t="n"/>
@@ -14428,7 +14434,7 @@
         <v/>
       </c>
       <c r="F41" s="17">
-        <f>IF(B41="","",IF(E41="还不错","种子-数学",IF(D41="完全没有","零基础",IF(E41="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B41="","",IF(TRIM(E41)="还不错","种子-数学",IF(TRIM(D41)="完全没有","零基础",IF(TRIM(E41)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G41" s="22" t="n"/>
@@ -14456,7 +14462,7 @@
         <v/>
       </c>
       <c r="F42" s="17">
-        <f>IF(B42="","",IF(E42="还不错","种子-数学",IF(D42="完全没有","零基础",IF(E42="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B42="","",IF(TRIM(E42)="还不错","种子-数学",IF(TRIM(D42)="完全没有","零基础",IF(TRIM(E42)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G42" s="22" t="n"/>
@@ -14484,7 +14490,7 @@
         <v/>
       </c>
       <c r="F43" s="17">
-        <f>IF(B43="","",IF(E43="还不错","种子-数学",IF(D43="完全没有","零基础",IF(E43="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B43="","",IF(TRIM(E43)="还不错","种子-数学",IF(TRIM(D43)="完全没有","零基础",IF(TRIM(E43)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G43" s="22" t="n"/>
@@ -14512,7 +14518,7 @@
         <v/>
       </c>
       <c r="F44" s="17">
-        <f>IF(B44="","",IF(E44="还不错","种子-数学",IF(D44="完全没有","零基础",IF(E44="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B44="","",IF(TRIM(E44)="还不错","种子-数学",IF(TRIM(D44)="完全没有","零基础",IF(TRIM(E44)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G44" s="22" t="n"/>
@@ -14540,7 +14546,7 @@
         <v/>
       </c>
       <c r="F45" s="17">
-        <f>IF(B45="","",IF(E45="还不错","种子-数学",IF(D45="完全没有","零基础",IF(E45="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B45="","",IF(TRIM(E45)="还不错","种子-数学",IF(TRIM(D45)="完全没有","零基础",IF(TRIM(E45)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G45" s="22" t="n"/>
@@ -14568,7 +14574,7 @@
         <v/>
       </c>
       <c r="F46" s="17">
-        <f>IF(B46="","",IF(E46="还不错","种子-数学",IF(D46="完全没有","零基础",IF(E46="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B46="","",IF(TRIM(E46)="还不错","种子-数学",IF(TRIM(D46)="完全没有","零基础",IF(TRIM(E46)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G46" s="22" t="n"/>
@@ -14596,7 +14602,7 @@
         <v/>
       </c>
       <c r="F47" s="17">
-        <f>IF(B47="","",IF(E47="还不错","种子-数学",IF(D47="完全没有","零基础",IF(E47="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B47="","",IF(TRIM(E47)="还不错","种子-数学",IF(TRIM(D47)="完全没有","零基础",IF(TRIM(E47)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G47" s="22" t="n"/>
@@ -14624,7 +14630,7 @@
         <v/>
       </c>
       <c r="F48" s="17">
-        <f>IF(B48="","",IF(E48="还不错","种子-数学",IF(D48="完全没有","零基础",IF(E48="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B48="","",IF(TRIM(E48)="还不错","种子-数学",IF(TRIM(D48)="完全没有","零基础",IF(TRIM(E48)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G48" s="22" t="n"/>
@@ -14652,7 +14658,7 @@
         <v/>
       </c>
       <c r="F49" s="17">
-        <f>IF(B49="","",IF(E49="还不错","种子-数学",IF(D49="完全没有","零基础",IF(E49="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B49="","",IF(TRIM(E49)="还不错","种子-数学",IF(TRIM(D49)="完全没有","零基础",IF(TRIM(E49)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G49" s="22" t="n"/>
@@ -14680,7 +14686,7 @@
         <v/>
       </c>
       <c r="F50" s="17">
-        <f>IF(B50="","",IF(E50="还不错","种子-数学",IF(D50="完全没有","零基础",IF(E50="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B50="","",IF(TRIM(E50)="还不错","种子-数学",IF(TRIM(D50)="完全没有","零基础",IF(TRIM(E50)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G50" s="22" t="n"/>
@@ -14708,7 +14714,7 @@
         <v/>
       </c>
       <c r="F51" s="17">
-        <f>IF(B51="","",IF(E51="还不错","种子-数学",IF(D51="完全没有","零基础",IF(E51="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B51="","",IF(TRIM(E51)="还不错","种子-数学",IF(TRIM(D51)="完全没有","零基础",IF(TRIM(E51)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G51" s="22" t="n"/>
@@ -14736,7 +14742,7 @@
         <v/>
       </c>
       <c r="F52" s="17">
-        <f>IF(B52="","",IF(E52="还不错","种子-数学",IF(D52="完全没有","零基础",IF(E52="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B52="","",IF(TRIM(E52)="还不错","种子-数学",IF(TRIM(D52)="完全没有","零基础",IF(TRIM(E52)="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G52" s="22" t="n"/>
@@ -14956,7 +14962,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>

--- a/90_通用工具_全学期复用/90-C4_学生档案汇总表_v2.4_20260820.xlsx
+++ b/90_通用工具_全学期复用/90-C4_学生档案汇总表_v2.4_20260820.xlsx
@@ -322,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -478,12 +478,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -885,7 +879,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B80"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -972,7 +966,7 @@
     <row r="13" ht="64" customHeight="1">
       <c r="A13" s="53" t="inlineStr">
         <is>
-          <t>课堂上不是举手加分。用 90-B2 点名器：视频放完抽 3 个人，说「册子举起来」，写了 2 分、写好或愿意念 5 分、空白跳过不说话。下课点「导出成绩表」。打地鼠用 90-B1，一局 12 题，每题约 12 秒，游戏里会显示 60～140 分——那是游戏分，不会直接加进周分，计算器会折成 0 / 2 / 5。作业不是书后课后题，你不用一本一本改。只有项目结束的收集表、或最难的加分题收集表，才打三档：没写 0、写了跑题 2、写了切题 5。没有收集表的那一周，作业列空着。</t>
+          <t>课堂上不是举手加分。用 90-B2 点名器：视频放完抽 3 个人，说「册子举起来」，写了 2 分、写好或愿意念 5 分、空白跳过不说话。下课点「导出成绩表」。打地鼠用 90-B1，一局 12 题，每题约 12 秒，游戏里的 60～140 分是游戏分，计算器会折成 0 / 2 / 5。现在不要另建「项目结束收集表」或「加分题收集表」。加分题就是主文档里那几道特别难的暂停点，课堂上举册子，写对 5 分。计算器 E、F 作业列先空着。</t>
         </is>
       </c>
     </row>
@@ -983,8 +977,8 @@
 1. 打开本文件，点最底下「本周计算器」。
 2. 点名器导出的表，找到最下面「本节汇总」（三列：姓名 / 组号 / 本节合计），贴到右边 S 列。
 3. 打地鼠导出的表，连表头贴到中间 J 列。D 列会自己变成 0、2 或 5。
-4. 如果这周有收集表，E、F 列手填 0 或 2 或 5；没有就空着。
-5. 「本周计算器」里表头黄色、写着「本周合计 ← 复制这一列」的那一列，复制 → 打开「每周积分」→ 粘到正在记的那一周（第1周就粘第1周，第5周才粘第5周）→ 右键「粘贴数值」。
+4. 作业列现在空着。加分题已经在课堂上用点名器加过了，不要再加一遍。
+5. 「本周计算器」里表头黄色、写着「本周合计 ← 复制这一列」的那一列，复制 → 打开「每周积分」→ 粘到正在记的那一周 → 右键「粘贴数值」。
 不要复制「每周积分」自己的 G 列。那一列表头是「第5周」。</t>
         </is>
       </c>
@@ -1248,16 +1242,16 @@
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="68" t="inlineStr">
-        <is>
-          <t>Q：作业布置什么？「项目最后一节收集表」「加分题」是什么？</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="72" customHeight="1">
-      <c r="A55" s="69" t="inlineStr">
-        <is>
-          <t>A：先把两句话拆开。它们都不是你刚做的开学点单。「加分题」= 主文档里写了「加分题」的那几个暂停点（项目一是第5题、第14题这种），学生写在记录册上，你抽 3 人举册子看，写对 5 分。不要另做企业微信。「项目最后一节收集表」= 以前设想过项目上完再发一张 3～5 题的短表。仓库里还没有现成的。你现在不必做。项目结束看点名器积分、评谁表现好就行。书后课后题不要收。没有短表的那一周，计算器作业列空着。</t>
+      <c r="A54" s="54" t="inlineStr">
+        <is>
+          <t>Q：作业布置什么？书后课后题吗？我还得一本一本改吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="52" customHeight="1">
+      <c r="A55" s="53" t="inlineStr">
+        <is>
+          <t>A：不要收书后课后题。加分题不是另做一张企业微信表——就是主文档里标了「加分题」的暂停点（项目一是第5、第11、第14暂停点），课堂上说「写出这个意思的，册子举起来」，写对 5 分。「每个项目最后一节的收集表」现在也不要建。开学点单是唯一必须建的企业微信表。计算器 E、F 列先空着。课堂上点名器已经加过的，不要再当作业加一遍。</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1466,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -1793,7 +1787,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AF52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2070,7 +2064,7 @@
         <v/>
       </c>
       <c r="AE3" s="10">
-        <f>IF(TRIM(V3&amp;"")="","",IF(OR(TRIM(V3)="不要用我的照片",TRIM(V3)="只给我自己看"),"★形象不可公开",IF(TRIM(V3)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V3="","",IF(OR(V3="不要用我的照片",V3="只给我自己看"),"★形象不可公开",IF(V3="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF3" s="8" t="n"/>
@@ -2116,7 +2110,7 @@
         <v/>
       </c>
       <c r="AE4" s="10">
-        <f>IF(TRIM(V4&amp;"")="","",IF(OR(TRIM(V4)="不要用我的照片",TRIM(V4)="只给我自己看"),"★形象不可公开",IF(TRIM(V4)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V4="","",IF(OR(V4="不要用我的照片",V4="只给我自己看"),"★形象不可公开",IF(V4="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF4" s="11" t="n"/>
@@ -2162,7 +2156,7 @@
         <v/>
       </c>
       <c r="AE5" s="10">
-        <f>IF(TRIM(V5&amp;"")="","",IF(OR(TRIM(V5)="不要用我的照片",TRIM(V5)="只给我自己看"),"★形象不可公开",IF(TRIM(V5)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V5="","",IF(OR(V5="不要用我的照片",V5="只给我自己看"),"★形象不可公开",IF(V5="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF5" s="8" t="n"/>
@@ -2208,7 +2202,7 @@
         <v/>
       </c>
       <c r="AE6" s="10">
-        <f>IF(TRIM(V6&amp;"")="","",IF(OR(TRIM(V6)="不要用我的照片",TRIM(V6)="只给我自己看"),"★形象不可公开",IF(TRIM(V6)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V6="","",IF(OR(V6="不要用我的照片",V6="只给我自己看"),"★形象不可公开",IF(V6="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF6" s="11" t="n"/>
@@ -2254,7 +2248,7 @@
         <v/>
       </c>
       <c r="AE7" s="10">
-        <f>IF(TRIM(V7&amp;"")="","",IF(OR(TRIM(V7)="不要用我的照片",TRIM(V7)="只给我自己看"),"★形象不可公开",IF(TRIM(V7)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V7="","",IF(OR(V7="不要用我的照片",V7="只给我自己看"),"★形象不可公开",IF(V7="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF7" s="8" t="n"/>
@@ -2300,7 +2294,7 @@
         <v/>
       </c>
       <c r="AE8" s="10">
-        <f>IF(TRIM(V8&amp;"")="","",IF(OR(TRIM(V8)="不要用我的照片",TRIM(V8)="只给我自己看"),"★形象不可公开",IF(TRIM(V8)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V8="","",IF(OR(V8="不要用我的照片",V8="只给我自己看"),"★形象不可公开",IF(V8="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF8" s="11" t="n"/>
@@ -2346,7 +2340,7 @@
         <v/>
       </c>
       <c r="AE9" s="10">
-        <f>IF(TRIM(V9&amp;"")="","",IF(OR(TRIM(V9)="不要用我的照片",TRIM(V9)="只给我自己看"),"★形象不可公开",IF(TRIM(V9)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V9="","",IF(OR(V9="不要用我的照片",V9="只给我自己看"),"★形象不可公开",IF(V9="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF9" s="8" t="n"/>
@@ -2392,7 +2386,7 @@
         <v/>
       </c>
       <c r="AE10" s="10">
-        <f>IF(TRIM(V10&amp;"")="","",IF(OR(TRIM(V10)="不要用我的照片",TRIM(V10)="只给我自己看"),"★形象不可公开",IF(TRIM(V10)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V10="","",IF(OR(V10="不要用我的照片",V10="只给我自己看"),"★形象不可公开",IF(V10="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF10" s="11" t="n"/>
@@ -2438,7 +2432,7 @@
         <v/>
       </c>
       <c r="AE11" s="10">
-        <f>IF(TRIM(V11&amp;"")="","",IF(OR(TRIM(V11)="不要用我的照片",TRIM(V11)="只给我自己看"),"★形象不可公开",IF(TRIM(V11)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V11="","",IF(OR(V11="不要用我的照片",V11="只给我自己看"),"★形象不可公开",IF(V11="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF11" s="8" t="n"/>
@@ -2484,7 +2478,7 @@
         <v/>
       </c>
       <c r="AE12" s="10">
-        <f>IF(TRIM(V12&amp;"")="","",IF(OR(TRIM(V12)="不要用我的照片",TRIM(V12)="只给我自己看"),"★形象不可公开",IF(TRIM(V12)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V12="","",IF(OR(V12="不要用我的照片",V12="只给我自己看"),"★形象不可公开",IF(V12="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF12" s="11" t="n"/>
@@ -2530,7 +2524,7 @@
         <v/>
       </c>
       <c r="AE13" s="10">
-        <f>IF(TRIM(V13&amp;"")="","",IF(OR(TRIM(V13)="不要用我的照片",TRIM(V13)="只给我自己看"),"★形象不可公开",IF(TRIM(V13)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V13="","",IF(OR(V13="不要用我的照片",V13="只给我自己看"),"★形象不可公开",IF(V13="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF13" s="8" t="n"/>
@@ -2576,7 +2570,7 @@
         <v/>
       </c>
       <c r="AE14" s="10">
-        <f>IF(TRIM(V14&amp;"")="","",IF(OR(TRIM(V14)="不要用我的照片",TRIM(V14)="只给我自己看"),"★形象不可公开",IF(TRIM(V14)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V14="","",IF(OR(V14="不要用我的照片",V14="只给我自己看"),"★形象不可公开",IF(V14="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF14" s="11" t="n"/>
@@ -2622,7 +2616,7 @@
         <v/>
       </c>
       <c r="AE15" s="10">
-        <f>IF(TRIM(V15&amp;"")="","",IF(OR(TRIM(V15)="不要用我的照片",TRIM(V15)="只给我自己看"),"★形象不可公开",IF(TRIM(V15)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V15="","",IF(OR(V15="不要用我的照片",V15="只给我自己看"),"★形象不可公开",IF(V15="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF15" s="8" t="n"/>
@@ -2668,7 +2662,7 @@
         <v/>
       </c>
       <c r="AE16" s="10">
-        <f>IF(TRIM(V16&amp;"")="","",IF(OR(TRIM(V16)="不要用我的照片",TRIM(V16)="只给我自己看"),"★形象不可公开",IF(TRIM(V16)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V16="","",IF(OR(V16="不要用我的照片",V16="只给我自己看"),"★形象不可公开",IF(V16="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF16" s="11" t="n"/>
@@ -2714,7 +2708,7 @@
         <v/>
       </c>
       <c r="AE17" s="10">
-        <f>IF(TRIM(V17&amp;"")="","",IF(OR(TRIM(V17)="不要用我的照片",TRIM(V17)="只给我自己看"),"★形象不可公开",IF(TRIM(V17)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V17="","",IF(OR(V17="不要用我的照片",V17="只给我自己看"),"★形象不可公开",IF(V17="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF17" s="8" t="n"/>
@@ -2760,7 +2754,7 @@
         <v/>
       </c>
       <c r="AE18" s="10">
-        <f>IF(TRIM(V18&amp;"")="","",IF(OR(TRIM(V18)="不要用我的照片",TRIM(V18)="只给我自己看"),"★形象不可公开",IF(TRIM(V18)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V18="","",IF(OR(V18="不要用我的照片",V18="只给我自己看"),"★形象不可公开",IF(V18="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF18" s="11" t="n"/>
@@ -2806,7 +2800,7 @@
         <v/>
       </c>
       <c r="AE19" s="10">
-        <f>IF(TRIM(V19&amp;"")="","",IF(OR(TRIM(V19)="不要用我的照片",TRIM(V19)="只给我自己看"),"★形象不可公开",IF(TRIM(V19)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V19="","",IF(OR(V19="不要用我的照片",V19="只给我自己看"),"★形象不可公开",IF(V19="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF19" s="8" t="n"/>
@@ -2852,7 +2846,7 @@
         <v/>
       </c>
       <c r="AE20" s="10">
-        <f>IF(TRIM(V20&amp;"")="","",IF(OR(TRIM(V20)="不要用我的照片",TRIM(V20)="只给我自己看"),"★形象不可公开",IF(TRIM(V20)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V20="","",IF(OR(V20="不要用我的照片",V20="只给我自己看"),"★形象不可公开",IF(V20="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF20" s="11" t="n"/>
@@ -2898,7 +2892,7 @@
         <v/>
       </c>
       <c r="AE21" s="10">
-        <f>IF(TRIM(V21&amp;"")="","",IF(OR(TRIM(V21)="不要用我的照片",TRIM(V21)="只给我自己看"),"★形象不可公开",IF(TRIM(V21)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V21="","",IF(OR(V21="不要用我的照片",V21="只给我自己看"),"★形象不可公开",IF(V21="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF21" s="8" t="n"/>
@@ -2944,7 +2938,7 @@
         <v/>
       </c>
       <c r="AE22" s="10">
-        <f>IF(TRIM(V22&amp;"")="","",IF(OR(TRIM(V22)="不要用我的照片",TRIM(V22)="只给我自己看"),"★形象不可公开",IF(TRIM(V22)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V22="","",IF(OR(V22="不要用我的照片",V22="只给我自己看"),"★形象不可公开",IF(V22="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF22" s="11" t="n"/>
@@ -2990,7 +2984,7 @@
         <v/>
       </c>
       <c r="AE23" s="10">
-        <f>IF(TRIM(V23&amp;"")="","",IF(OR(TRIM(V23)="不要用我的照片",TRIM(V23)="只给我自己看"),"★形象不可公开",IF(TRIM(V23)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V23="","",IF(OR(V23="不要用我的照片",V23="只给我自己看"),"★形象不可公开",IF(V23="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF23" s="8" t="n"/>
@@ -3036,7 +3030,7 @@
         <v/>
       </c>
       <c r="AE24" s="10">
-        <f>IF(TRIM(V24&amp;"")="","",IF(OR(TRIM(V24)="不要用我的照片",TRIM(V24)="只给我自己看"),"★形象不可公开",IF(TRIM(V24)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V24="","",IF(OR(V24="不要用我的照片",V24="只给我自己看"),"★形象不可公开",IF(V24="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF24" s="11" t="n"/>
@@ -3082,7 +3076,7 @@
         <v/>
       </c>
       <c r="AE25" s="10">
-        <f>IF(TRIM(V25&amp;"")="","",IF(OR(TRIM(V25)="不要用我的照片",TRIM(V25)="只给我自己看"),"★形象不可公开",IF(TRIM(V25)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V25="","",IF(OR(V25="不要用我的照片",V25="只给我自己看"),"★形象不可公开",IF(V25="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF25" s="8" t="n"/>
@@ -3128,7 +3122,7 @@
         <v/>
       </c>
       <c r="AE26" s="10">
-        <f>IF(TRIM(V26&amp;"")="","",IF(OR(TRIM(V26)="不要用我的照片",TRIM(V26)="只给我自己看"),"★形象不可公开",IF(TRIM(V26)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V26="","",IF(OR(V26="不要用我的照片",V26="只给我自己看"),"★形象不可公开",IF(V26="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF26" s="11" t="n"/>
@@ -3174,7 +3168,7 @@
         <v/>
       </c>
       <c r="AE27" s="10">
-        <f>IF(TRIM(V27&amp;"")="","",IF(OR(TRIM(V27)="不要用我的照片",TRIM(V27)="只给我自己看"),"★形象不可公开",IF(TRIM(V27)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V27="","",IF(OR(V27="不要用我的照片",V27="只给我自己看"),"★形象不可公开",IF(V27="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF27" s="8" t="n"/>
@@ -3220,7 +3214,7 @@
         <v/>
       </c>
       <c r="AE28" s="10">
-        <f>IF(TRIM(V28&amp;"")="","",IF(OR(TRIM(V28)="不要用我的照片",TRIM(V28)="只给我自己看"),"★形象不可公开",IF(TRIM(V28)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V28="","",IF(OR(V28="不要用我的照片",V28="只给我自己看"),"★形象不可公开",IF(V28="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF28" s="11" t="n"/>
@@ -3266,7 +3260,7 @@
         <v/>
       </c>
       <c r="AE29" s="10">
-        <f>IF(TRIM(V29&amp;"")="","",IF(OR(TRIM(V29)="不要用我的照片",TRIM(V29)="只给我自己看"),"★形象不可公开",IF(TRIM(V29)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V29="","",IF(OR(V29="不要用我的照片",V29="只给我自己看"),"★形象不可公开",IF(V29="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF29" s="8" t="n"/>
@@ -3312,7 +3306,7 @@
         <v/>
       </c>
       <c r="AE30" s="10">
-        <f>IF(TRIM(V30&amp;"")="","",IF(OR(TRIM(V30)="不要用我的照片",TRIM(V30)="只给我自己看"),"★形象不可公开",IF(TRIM(V30)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V30="","",IF(OR(V30="不要用我的照片",V30="只给我自己看"),"★形象不可公开",IF(V30="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF30" s="11" t="n"/>
@@ -3358,7 +3352,7 @@
         <v/>
       </c>
       <c r="AE31" s="10">
-        <f>IF(TRIM(V31&amp;"")="","",IF(OR(TRIM(V31)="不要用我的照片",TRIM(V31)="只给我自己看"),"★形象不可公开",IF(TRIM(V31)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V31="","",IF(OR(V31="不要用我的照片",V31="只给我自己看"),"★形象不可公开",IF(V31="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF31" s="8" t="n"/>
@@ -3404,7 +3398,7 @@
         <v/>
       </c>
       <c r="AE32" s="10">
-        <f>IF(TRIM(V32&amp;"")="","",IF(OR(TRIM(V32)="不要用我的照片",TRIM(V32)="只给我自己看"),"★形象不可公开",IF(TRIM(V32)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V32="","",IF(OR(V32="不要用我的照片",V32="只给我自己看"),"★形象不可公开",IF(V32="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF32" s="11" t="n"/>
@@ -3450,7 +3444,7 @@
         <v/>
       </c>
       <c r="AE33" s="10">
-        <f>IF(TRIM(V33&amp;"")="","",IF(OR(TRIM(V33)="不要用我的照片",TRIM(V33)="只给我自己看"),"★形象不可公开",IF(TRIM(V33)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V33="","",IF(OR(V33="不要用我的照片",V33="只给我自己看"),"★形象不可公开",IF(V33="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF33" s="8" t="n"/>
@@ -3496,7 +3490,7 @@
         <v/>
       </c>
       <c r="AE34" s="10">
-        <f>IF(TRIM(V34&amp;"")="","",IF(OR(TRIM(V34)="不要用我的照片",TRIM(V34)="只给我自己看"),"★形象不可公开",IF(TRIM(V34)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V34="","",IF(OR(V34="不要用我的照片",V34="只给我自己看"),"★形象不可公开",IF(V34="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF34" s="11" t="n"/>
@@ -3542,7 +3536,7 @@
         <v/>
       </c>
       <c r="AE35" s="10">
-        <f>IF(TRIM(V35&amp;"")="","",IF(OR(TRIM(V35)="不要用我的照片",TRIM(V35)="只给我自己看"),"★形象不可公开",IF(TRIM(V35)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V35="","",IF(OR(V35="不要用我的照片",V35="只给我自己看"),"★形象不可公开",IF(V35="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF35" s="8" t="n"/>
@@ -3588,7 +3582,7 @@
         <v/>
       </c>
       <c r="AE36" s="10">
-        <f>IF(TRIM(V36&amp;"")="","",IF(OR(TRIM(V36)="不要用我的照片",TRIM(V36)="只给我自己看"),"★形象不可公开",IF(TRIM(V36)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V36="","",IF(OR(V36="不要用我的照片",V36="只给我自己看"),"★形象不可公开",IF(V36="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF36" s="11" t="n"/>
@@ -3634,7 +3628,7 @@
         <v/>
       </c>
       <c r="AE37" s="10">
-        <f>IF(TRIM(V37&amp;"")="","",IF(OR(TRIM(V37)="不要用我的照片",TRIM(V37)="只给我自己看"),"★形象不可公开",IF(TRIM(V37)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V37="","",IF(OR(V37="不要用我的照片",V37="只给我自己看"),"★形象不可公开",IF(V37="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF37" s="8" t="n"/>
@@ -3680,7 +3674,7 @@
         <v/>
       </c>
       <c r="AE38" s="10">
-        <f>IF(TRIM(V38&amp;"")="","",IF(OR(TRIM(V38)="不要用我的照片",TRIM(V38)="只给我自己看"),"★形象不可公开",IF(TRIM(V38)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V38="","",IF(OR(V38="不要用我的照片",V38="只给我自己看"),"★形象不可公开",IF(V38="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF38" s="11" t="n"/>
@@ -3726,7 +3720,7 @@
         <v/>
       </c>
       <c r="AE39" s="10">
-        <f>IF(TRIM(V39&amp;"")="","",IF(OR(TRIM(V39)="不要用我的照片",TRIM(V39)="只给我自己看"),"★形象不可公开",IF(TRIM(V39)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V39="","",IF(OR(V39="不要用我的照片",V39="只给我自己看"),"★形象不可公开",IF(V39="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF39" s="8" t="n"/>
@@ -3772,7 +3766,7 @@
         <v/>
       </c>
       <c r="AE40" s="10">
-        <f>IF(TRIM(V40&amp;"")="","",IF(OR(TRIM(V40)="不要用我的照片",TRIM(V40)="只给我自己看"),"★形象不可公开",IF(TRIM(V40)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V40="","",IF(OR(V40="不要用我的照片",V40="只给我自己看"),"★形象不可公开",IF(V40="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF40" s="11" t="n"/>
@@ -3818,7 +3812,7 @@
         <v/>
       </c>
       <c r="AE41" s="10">
-        <f>IF(TRIM(V41&amp;"")="","",IF(OR(TRIM(V41)="不要用我的照片",TRIM(V41)="只给我自己看"),"★形象不可公开",IF(TRIM(V41)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V41="","",IF(OR(V41="不要用我的照片",V41="只给我自己看"),"★形象不可公开",IF(V41="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF41" s="8" t="n"/>
@@ -3864,7 +3858,7 @@
         <v/>
       </c>
       <c r="AE42" s="10">
-        <f>IF(TRIM(V42&amp;"")="","",IF(OR(TRIM(V42)="不要用我的照片",TRIM(V42)="只给我自己看"),"★形象不可公开",IF(TRIM(V42)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V42="","",IF(OR(V42="不要用我的照片",V42="只给我自己看"),"★形象不可公开",IF(V42="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF42" s="11" t="n"/>
@@ -3910,7 +3904,7 @@
         <v/>
       </c>
       <c r="AE43" s="10">
-        <f>IF(TRIM(V43&amp;"")="","",IF(OR(TRIM(V43)="不要用我的照片",TRIM(V43)="只给我自己看"),"★形象不可公开",IF(TRIM(V43)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V43="","",IF(OR(V43="不要用我的照片",V43="只给我自己看"),"★形象不可公开",IF(V43="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF43" s="8" t="n"/>
@@ -3956,7 +3950,7 @@
         <v/>
       </c>
       <c r="AE44" s="10">
-        <f>IF(TRIM(V44&amp;"")="","",IF(OR(TRIM(V44)="不要用我的照片",TRIM(V44)="只给我自己看"),"★形象不可公开",IF(TRIM(V44)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V44="","",IF(OR(V44="不要用我的照片",V44="只给我自己看"),"★形象不可公开",IF(V44="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF44" s="11" t="n"/>
@@ -4002,7 +3996,7 @@
         <v/>
       </c>
       <c r="AE45" s="10">
-        <f>IF(TRIM(V45&amp;"")="","",IF(OR(TRIM(V45)="不要用我的照片",TRIM(V45)="只给我自己看"),"★形象不可公开",IF(TRIM(V45)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V45="","",IF(OR(V45="不要用我的照片",V45="只给我自己看"),"★形象不可公开",IF(V45="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF45" s="8" t="n"/>
@@ -4048,7 +4042,7 @@
         <v/>
       </c>
       <c r="AE46" s="10">
-        <f>IF(TRIM(V46&amp;"")="","",IF(OR(TRIM(V46)="不要用我的照片",TRIM(V46)="只给我自己看"),"★形象不可公开",IF(TRIM(V46)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V46="","",IF(OR(V46="不要用我的照片",V46="只给我自己看"),"★形象不可公开",IF(V46="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF46" s="11" t="n"/>
@@ -4094,7 +4088,7 @@
         <v/>
       </c>
       <c r="AE47" s="10">
-        <f>IF(TRIM(V47&amp;"")="","",IF(OR(TRIM(V47)="不要用我的照片",TRIM(V47)="只给我自己看"),"★形象不可公开",IF(TRIM(V47)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V47="","",IF(OR(V47="不要用我的照片",V47="只给我自己看"),"★形象不可公开",IF(V47="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF47" s="8" t="n"/>
@@ -4140,7 +4134,7 @@
         <v/>
       </c>
       <c r="AE48" s="10">
-        <f>IF(TRIM(V48&amp;"")="","",IF(OR(TRIM(V48)="不要用我的照片",TRIM(V48)="只给我自己看"),"★形象不可公开",IF(TRIM(V48)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V48="","",IF(OR(V48="不要用我的照片",V48="只给我自己看"),"★形象不可公开",IF(V48="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF48" s="11" t="n"/>
@@ -4186,7 +4180,7 @@
         <v/>
       </c>
       <c r="AE49" s="10">
-        <f>IF(TRIM(V49&amp;"")="","",IF(OR(TRIM(V49)="不要用我的照片",TRIM(V49)="只给我自己看"),"★形象不可公开",IF(TRIM(V49)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V49="","",IF(OR(V49="不要用我的照片",V49="只给我自己看"),"★形象不可公开",IF(V49="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF49" s="8" t="n"/>
@@ -4232,7 +4226,7 @@
         <v/>
       </c>
       <c r="AE50" s="10">
-        <f>IF(TRIM(V50&amp;"")="","",IF(OR(TRIM(V50)="不要用我的照片",TRIM(V50)="只给我自己看"),"★形象不可公开",IF(TRIM(V50)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V50="","",IF(OR(V50="不要用我的照片",V50="只给我自己看"),"★形象不可公开",IF(V50="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF50" s="11" t="n"/>
@@ -4278,7 +4272,7 @@
         <v/>
       </c>
       <c r="AE51" s="10">
-        <f>IF(TRIM(V51&amp;"")="","",IF(OR(TRIM(V51)="不要用我的照片",TRIM(V51)="只给我自己看"),"★形象不可公开",IF(TRIM(V51)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V51="","",IF(OR(V51="不要用我的照片",V51="只给我自己看"),"★形象不可公开",IF(V51="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF51" s="8" t="n"/>
@@ -4324,7 +4318,7 @@
         <v/>
       </c>
       <c r="AE52" s="10">
-        <f>IF(TRIM(V52&amp;"")="","",IF(OR(TRIM(V52)="不要用我的照片",TRIM(V52)="只给我自己看"),"★形象不可公开",IF(TRIM(V52)="可以但别画太丑","只用奖励风格","可正常使用")))</f>
+        <f>IF(V52="","",IF(OR(V52="不要用我的照片",V52="只给我自己看"),"★形象不可公开",IF(V52="可以但别画太丑","只用奖励风格","可正常使用")))</f>
         <v/>
       </c>
       <c r="AF52" s="11" t="n"/>
@@ -4371,7 +4365,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -6369,7 +6363,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U131"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -6395,7 +6389,7 @@
     <row r="1" ht="78" customHeight="1">
       <c r="A1" s="66" t="inlineStr">
         <is>
-          <t>这张表就在本文件底下，点「本周计算器」进去。用处：把这一周三处的分加总，得出「本周合计」。①点名器 90-B2 导出的表，找到最下面「本节汇总」（姓名/组号/本节合计），贴到右边 S 列；②打地鼠 90-B1 导出的表贴到中间 J 列（含表头）。游戏里的 100 多分不会直接加进来，D 列会自动折成 0 / 2 / 5；③作业不是书后课后题。只有「项目结束的收集表」或「加分题收集表」才打分：没写 0、写了跑题 2、写了切题 5。没有收集表的那一周，E、F 列空着；④表头黄色的「本周合计 ← 复制这一列」，复制后到「每周积分」正在记的那一周，右键粘贴数值。不要粘到「每周积分」的 G 列——那是第5周。</t>
+          <t>这张表就在本文件底下，点「本周计算器」进去。用处：把这一周课堂分、打地鼠折算分加总，得出「本周合计」。①点名器 90-B2 导出的表，找到最下面「本节汇总」（姓名/组号/本节合计），贴到右边 S 列；②打地鼠 90-B1 导出的表贴到中间 J 列（含表头）。游戏里的 100 多分不会直接加进来，D 列会自动折成 0 / 2 / 5；③作业列现在空着。加分题在课堂上举册子已经加过了，不要另建收集表；④表头黄色的「本周合计 ← 复制这一列」，复制后到「每周积分」正在记的那一周，右键粘贴数值。不要粘到「每周积分」的 G 列——那是第5周。</t>
         </is>
       </c>
       <c r="B1" s="46" t="n"/>
@@ -9513,7 +9507,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -10851,7 +10845,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -11917,7 +11911,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -13140,7 +13134,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M80"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -13163,7 +13157,8 @@
           <t>问卷贴进「学生档案」之后再来。现在左边空着、F 列没有标签，正常——标签是贴完第1题第2题才自动打的，学期一开始没有。
 这张表不会自动分组。你只填 G 列（蓝色下拉）。不要让学委分组，学委会把熟人放一起。学委只帮核对宿舍号。
 填法：先把 F 列「种子-数学」每人分到不同组 → 再把「零基础」每人分到不同组 → 「需帮扶」跟着种子走 → 剩下的人往人少的组填。同宿舍能一起就一起。
-填完看右边：每组「种子」不能是 0，「零基础」不能是 0。上课说一句即可：你们这组叫出纳组，管钱的。不用讲岗位课。桌签 90-C10。</t>
+填完看右边：每组「种子」不能是 0，「零基础」不能是 0。上课说一句即可：你们这组叫出纳组，管钱的。不用讲岗位课。桌签 90-C10。
+不要按组布置课后作业。出纳组、记账组不是作业标签。组的任务只出现在课堂上：打地鼠按组上台、填凭证时出纳组先填收付款、审核组审别人的。种子/零基础只给你看，不要跟学生说。</t>
         </is>
       </c>
       <c r="B1" s="46" t="n"/>
@@ -13263,7 +13258,7 @@
         <v/>
       </c>
       <c r="F3" s="17">
-        <f>IF(B3="","",IF(TRIM(E3)="还不错","种子-数学",IF(TRIM(D3)="完全没有","零基础",IF(TRIM(E3)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B3="","",IF(E3="还不错","种子-数学",IF(D3="完全没有","零基础",IF(E3="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G3" s="22" t="n"/>
@@ -13308,7 +13303,7 @@
         <v/>
       </c>
       <c r="F4" s="17">
-        <f>IF(B4="","",IF(TRIM(E4)="还不错","种子-数学",IF(TRIM(D4)="完全没有","零基础",IF(TRIM(E4)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B4="","",IF(E4="还不错","种子-数学",IF(D4="完全没有","零基础",IF(E4="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G4" s="22" t="n"/>
@@ -13353,7 +13348,7 @@
         <v/>
       </c>
       <c r="F5" s="17">
-        <f>IF(B5="","",IF(TRIM(E5)="还不错","种子-数学",IF(TRIM(D5)="完全没有","零基础",IF(TRIM(E5)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B5="","",IF(E5="还不错","种子-数学",IF(D5="完全没有","零基础",IF(E5="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G5" s="22" t="n"/>
@@ -13398,7 +13393,7 @@
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>IF(B6="","",IF(TRIM(E6)="还不错","种子-数学",IF(TRIM(D6)="完全没有","零基础",IF(TRIM(E6)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B6="","",IF(E6="还不错","种子-数学",IF(D6="完全没有","零基础",IF(E6="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G6" s="22" t="n"/>
@@ -13443,7 +13438,7 @@
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>IF(B7="","",IF(TRIM(E7)="还不错","种子-数学",IF(TRIM(D7)="完全没有","零基础",IF(TRIM(E7)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B7="","",IF(E7="还不错","种子-数学",IF(D7="完全没有","零基础",IF(E7="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G7" s="22" t="n"/>
@@ -13488,7 +13483,7 @@
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>IF(B8="","",IF(TRIM(E8)="还不错","种子-数学",IF(TRIM(D8)="完全没有","零基础",IF(TRIM(E8)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B8="","",IF(E8="还不错","种子-数学",IF(D8="完全没有","零基础",IF(E8="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G8" s="22" t="n"/>
@@ -13533,7 +13528,7 @@
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>IF(B9="","",IF(TRIM(E9)="还不错","种子-数学",IF(TRIM(D9)="完全没有","零基础",IF(TRIM(E9)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B9="","",IF(E9="还不错","种子-数学",IF(D9="完全没有","零基础",IF(E9="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G9" s="22" t="n"/>
@@ -13561,7 +13556,7 @@
         <v/>
       </c>
       <c r="F10" s="17">
-        <f>IF(B10="","",IF(TRIM(E10)="还不错","种子-数学",IF(TRIM(D10)="完全没有","零基础",IF(TRIM(E10)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B10="","",IF(E10="还不错","种子-数学",IF(D10="完全没有","零基础",IF(E10="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G10" s="22" t="n"/>
@@ -13594,7 +13589,7 @@
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>IF(B11="","",IF(TRIM(E11)="还不错","种子-数学",IF(TRIM(D11)="完全没有","零基础",IF(TRIM(E11)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B11="","",IF(E11="还不错","种子-数学",IF(D11="完全没有","零基础",IF(E11="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G11" s="22" t="n"/>
@@ -13622,7 +13617,7 @@
         <v/>
       </c>
       <c r="F12" s="17">
-        <f>IF(B12="","",IF(TRIM(E12)="还不错","种子-数学",IF(TRIM(D12)="完全没有","零基础",IF(TRIM(E12)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B12="","",IF(E12="还不错","种子-数学",IF(D12="完全没有","零基础",IF(E12="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G12" s="22" t="n"/>
@@ -13650,7 +13645,7 @@
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>IF(B13="","",IF(TRIM(E13)="还不错","种子-数学",IF(TRIM(D13)="完全没有","零基础",IF(TRIM(E13)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B13="","",IF(E13="还不错","种子-数学",IF(D13="完全没有","零基础",IF(E13="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G13" s="22" t="n"/>
@@ -13678,7 +13673,7 @@
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>IF(B14="","",IF(TRIM(E14)="还不错","种子-数学",IF(TRIM(D14)="完全没有","零基础",IF(TRIM(E14)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B14="","",IF(E14="还不错","种子-数学",IF(D14="完全没有","零基础",IF(E14="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G14" s="22" t="n"/>
@@ -13706,7 +13701,7 @@
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>IF(B15="","",IF(TRIM(E15)="还不错","种子-数学",IF(TRIM(D15)="完全没有","零基础",IF(TRIM(E15)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B15="","",IF(E15="还不错","种子-数学",IF(D15="完全没有","零基础",IF(E15="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G15" s="22" t="n"/>
@@ -13734,7 +13729,7 @@
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>IF(B16="","",IF(TRIM(E16)="还不错","种子-数学",IF(TRIM(D16)="完全没有","零基础",IF(TRIM(E16)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B16="","",IF(E16="还不错","种子-数学",IF(D16="完全没有","零基础",IF(E16="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G16" s="22" t="n"/>
@@ -13762,7 +13757,7 @@
         <v/>
       </c>
       <c r="F17" s="17">
-        <f>IF(B17="","",IF(TRIM(E17)="还不错","种子-数学",IF(TRIM(D17)="完全没有","零基础",IF(TRIM(E17)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B17="","",IF(E17="还不错","种子-数学",IF(D17="完全没有","零基础",IF(E17="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G17" s="22" t="n"/>
@@ -13790,7 +13785,7 @@
         <v/>
       </c>
       <c r="F18" s="17">
-        <f>IF(B18="","",IF(TRIM(E18)="还不错","种子-数学",IF(TRIM(D18)="完全没有","零基础",IF(TRIM(E18)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B18="","",IF(E18="还不错","种子-数学",IF(D18="完全没有","零基础",IF(E18="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G18" s="22" t="n"/>
@@ -13818,7 +13813,7 @@
         <v/>
       </c>
       <c r="F19" s="17">
-        <f>IF(B19="","",IF(TRIM(E19)="还不错","种子-数学",IF(TRIM(D19)="完全没有","零基础",IF(TRIM(E19)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B19="","",IF(E19="还不错","种子-数学",IF(D19="完全没有","零基础",IF(E19="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G19" s="22" t="n"/>
@@ -13846,7 +13841,7 @@
         <v/>
       </c>
       <c r="F20" s="17">
-        <f>IF(B20="","",IF(TRIM(E20)="还不错","种子-数学",IF(TRIM(D20)="完全没有","零基础",IF(TRIM(E20)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B20="","",IF(E20="还不错","种子-数学",IF(D20="完全没有","零基础",IF(E20="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G20" s="22" t="n"/>
@@ -13874,7 +13869,7 @@
         <v/>
       </c>
       <c r="F21" s="17">
-        <f>IF(B21="","",IF(TRIM(E21)="还不错","种子-数学",IF(TRIM(D21)="完全没有","零基础",IF(TRIM(E21)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B21="","",IF(E21="还不错","种子-数学",IF(D21="完全没有","零基础",IF(E21="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G21" s="22" t="n"/>
@@ -13902,7 +13897,7 @@
         <v/>
       </c>
       <c r="F22" s="17">
-        <f>IF(B22="","",IF(TRIM(E22)="还不错","种子-数学",IF(TRIM(D22)="完全没有","零基础",IF(TRIM(E22)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B22="","",IF(E22="还不错","种子-数学",IF(D22="完全没有","零基础",IF(E22="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G22" s="22" t="n"/>
@@ -13930,7 +13925,7 @@
         <v/>
       </c>
       <c r="F23" s="17">
-        <f>IF(B23="","",IF(TRIM(E23)="还不错","种子-数学",IF(TRIM(D23)="完全没有","零基础",IF(TRIM(E23)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B23="","",IF(E23="还不错","种子-数学",IF(D23="完全没有","零基础",IF(E23="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G23" s="22" t="n"/>
@@ -13958,7 +13953,7 @@
         <v/>
       </c>
       <c r="F24" s="17">
-        <f>IF(B24="","",IF(TRIM(E24)="还不错","种子-数学",IF(TRIM(D24)="完全没有","零基础",IF(TRIM(E24)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B24="","",IF(E24="还不错","种子-数学",IF(D24="完全没有","零基础",IF(E24="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G24" s="22" t="n"/>
@@ -13986,7 +13981,7 @@
         <v/>
       </c>
       <c r="F25" s="17">
-        <f>IF(B25="","",IF(TRIM(E25)="还不错","种子-数学",IF(TRIM(D25)="完全没有","零基础",IF(TRIM(E25)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B25="","",IF(E25="还不错","种子-数学",IF(D25="完全没有","零基础",IF(E25="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G25" s="22" t="n"/>
@@ -14014,7 +14009,7 @@
         <v/>
       </c>
       <c r="F26" s="17">
-        <f>IF(B26="","",IF(TRIM(E26)="还不错","种子-数学",IF(TRIM(D26)="完全没有","零基础",IF(TRIM(E26)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B26="","",IF(E26="还不错","种子-数学",IF(D26="完全没有","零基础",IF(E26="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G26" s="22" t="n"/>
@@ -14042,7 +14037,7 @@
         <v/>
       </c>
       <c r="F27" s="17">
-        <f>IF(B27="","",IF(TRIM(E27)="还不错","种子-数学",IF(TRIM(D27)="完全没有","零基础",IF(TRIM(E27)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B27="","",IF(E27="还不错","种子-数学",IF(D27="完全没有","零基础",IF(E27="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G27" s="22" t="n"/>
@@ -14070,7 +14065,7 @@
         <v/>
       </c>
       <c r="F28" s="17">
-        <f>IF(B28="","",IF(TRIM(E28)="还不错","种子-数学",IF(TRIM(D28)="完全没有","零基础",IF(TRIM(E28)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B28="","",IF(E28="还不错","种子-数学",IF(D28="完全没有","零基础",IF(E28="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G28" s="22" t="n"/>
@@ -14098,7 +14093,7 @@
         <v/>
       </c>
       <c r="F29" s="17">
-        <f>IF(B29="","",IF(TRIM(E29)="还不错","种子-数学",IF(TRIM(D29)="完全没有","零基础",IF(TRIM(E29)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B29="","",IF(E29="还不错","种子-数学",IF(D29="完全没有","零基础",IF(E29="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G29" s="22" t="n"/>
@@ -14126,7 +14121,7 @@
         <v/>
       </c>
       <c r="F30" s="17">
-        <f>IF(B30="","",IF(TRIM(E30)="还不错","种子-数学",IF(TRIM(D30)="完全没有","零基础",IF(TRIM(E30)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B30="","",IF(E30="还不错","种子-数学",IF(D30="完全没有","零基础",IF(E30="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G30" s="22" t="n"/>
@@ -14154,7 +14149,7 @@
         <v/>
       </c>
       <c r="F31" s="17">
-        <f>IF(B31="","",IF(TRIM(E31)="还不错","种子-数学",IF(TRIM(D31)="完全没有","零基础",IF(TRIM(E31)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B31="","",IF(E31="还不错","种子-数学",IF(D31="完全没有","零基础",IF(E31="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G31" s="22" t="n"/>
@@ -14182,7 +14177,7 @@
         <v/>
       </c>
       <c r="F32" s="17">
-        <f>IF(B32="","",IF(TRIM(E32)="还不错","种子-数学",IF(TRIM(D32)="完全没有","零基础",IF(TRIM(E32)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B32="","",IF(E32="还不错","种子-数学",IF(D32="完全没有","零基础",IF(E32="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G32" s="22" t="n"/>
@@ -14210,7 +14205,7 @@
         <v/>
       </c>
       <c r="F33" s="17">
-        <f>IF(B33="","",IF(TRIM(E33)="还不错","种子-数学",IF(TRIM(D33)="完全没有","零基础",IF(TRIM(E33)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B33="","",IF(E33="还不错","种子-数学",IF(D33="完全没有","零基础",IF(E33="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G33" s="22" t="n"/>
@@ -14238,7 +14233,7 @@
         <v/>
       </c>
       <c r="F34" s="17">
-        <f>IF(B34="","",IF(TRIM(E34)="还不错","种子-数学",IF(TRIM(D34)="完全没有","零基础",IF(TRIM(E34)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B34="","",IF(E34="还不错","种子-数学",IF(D34="完全没有","零基础",IF(E34="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G34" s="22" t="n"/>
@@ -14266,7 +14261,7 @@
         <v/>
       </c>
       <c r="F35" s="17">
-        <f>IF(B35="","",IF(TRIM(E35)="还不错","种子-数学",IF(TRIM(D35)="完全没有","零基础",IF(TRIM(E35)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B35="","",IF(E35="还不错","种子-数学",IF(D35="完全没有","零基础",IF(E35="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G35" s="22" t="n"/>
@@ -14294,7 +14289,7 @@
         <v/>
       </c>
       <c r="F36" s="17">
-        <f>IF(B36="","",IF(TRIM(E36)="还不错","种子-数学",IF(TRIM(D36)="完全没有","零基础",IF(TRIM(E36)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B36="","",IF(E36="还不错","种子-数学",IF(D36="完全没有","零基础",IF(E36="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G36" s="22" t="n"/>
@@ -14322,7 +14317,7 @@
         <v/>
       </c>
       <c r="F37" s="17">
-        <f>IF(B37="","",IF(TRIM(E37)="还不错","种子-数学",IF(TRIM(D37)="完全没有","零基础",IF(TRIM(E37)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B37="","",IF(E37="还不错","种子-数学",IF(D37="完全没有","零基础",IF(E37="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G37" s="22" t="n"/>
@@ -14350,7 +14345,7 @@
         <v/>
       </c>
       <c r="F38" s="17">
-        <f>IF(B38="","",IF(TRIM(E38)="还不错","种子-数学",IF(TRIM(D38)="完全没有","零基础",IF(TRIM(E38)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B38="","",IF(E38="还不错","种子-数学",IF(D38="完全没有","零基础",IF(E38="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G38" s="22" t="n"/>
@@ -14378,7 +14373,7 @@
         <v/>
       </c>
       <c r="F39" s="17">
-        <f>IF(B39="","",IF(TRIM(E39)="还不错","种子-数学",IF(TRIM(D39)="完全没有","零基础",IF(TRIM(E39)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B39="","",IF(E39="还不错","种子-数学",IF(D39="完全没有","零基础",IF(E39="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G39" s="22" t="n"/>
@@ -14406,7 +14401,7 @@
         <v/>
       </c>
       <c r="F40" s="17">
-        <f>IF(B40="","",IF(TRIM(E40)="还不错","种子-数学",IF(TRIM(D40)="完全没有","零基础",IF(TRIM(E40)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B40="","",IF(E40="还不错","种子-数学",IF(D40="完全没有","零基础",IF(E40="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G40" s="22" t="n"/>
@@ -14434,7 +14429,7 @@
         <v/>
       </c>
       <c r="F41" s="17">
-        <f>IF(B41="","",IF(TRIM(E41)="还不错","种子-数学",IF(TRIM(D41)="完全没有","零基础",IF(TRIM(E41)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B41="","",IF(E41="还不错","种子-数学",IF(D41="完全没有","零基础",IF(E41="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G41" s="22" t="n"/>
@@ -14462,7 +14457,7 @@
         <v/>
       </c>
       <c r="F42" s="17">
-        <f>IF(B42="","",IF(TRIM(E42)="还不错","种子-数学",IF(TRIM(D42)="完全没有","零基础",IF(TRIM(E42)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B42="","",IF(E42="还不错","种子-数学",IF(D42="完全没有","零基础",IF(E42="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G42" s="22" t="n"/>
@@ -14490,7 +14485,7 @@
         <v/>
       </c>
       <c r="F43" s="17">
-        <f>IF(B43="","",IF(TRIM(E43)="还不错","种子-数学",IF(TRIM(D43)="完全没有","零基础",IF(TRIM(E43)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B43="","",IF(E43="还不错","种子-数学",IF(D43="完全没有","零基础",IF(E43="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G43" s="22" t="n"/>
@@ -14518,7 +14513,7 @@
         <v/>
       </c>
       <c r="F44" s="17">
-        <f>IF(B44="","",IF(TRIM(E44)="还不错","种子-数学",IF(TRIM(D44)="完全没有","零基础",IF(TRIM(E44)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B44="","",IF(E44="还不错","种子-数学",IF(D44="完全没有","零基础",IF(E44="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G44" s="22" t="n"/>
@@ -14546,7 +14541,7 @@
         <v/>
       </c>
       <c r="F45" s="17">
-        <f>IF(B45="","",IF(TRIM(E45)="还不错","种子-数学",IF(TRIM(D45)="完全没有","零基础",IF(TRIM(E45)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B45="","",IF(E45="还不错","种子-数学",IF(D45="完全没有","零基础",IF(E45="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G45" s="22" t="n"/>
@@ -14574,7 +14569,7 @@
         <v/>
       </c>
       <c r="F46" s="17">
-        <f>IF(B46="","",IF(TRIM(E46)="还不错","种子-数学",IF(TRIM(D46)="完全没有","零基础",IF(TRIM(E46)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B46="","",IF(E46="还不错","种子-数学",IF(D46="完全没有","零基础",IF(E46="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G46" s="22" t="n"/>
@@ -14602,7 +14597,7 @@
         <v/>
       </c>
       <c r="F47" s="17">
-        <f>IF(B47="","",IF(TRIM(E47)="还不错","种子-数学",IF(TRIM(D47)="完全没有","零基础",IF(TRIM(E47)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B47="","",IF(E47="还不错","种子-数学",IF(D47="完全没有","零基础",IF(E47="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G47" s="22" t="n"/>
@@ -14630,7 +14625,7 @@
         <v/>
       </c>
       <c r="F48" s="17">
-        <f>IF(B48="","",IF(TRIM(E48)="还不错","种子-数学",IF(TRIM(D48)="完全没有","零基础",IF(TRIM(E48)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B48="","",IF(E48="还不错","种子-数学",IF(D48="完全没有","零基础",IF(E48="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G48" s="22" t="n"/>
@@ -14658,7 +14653,7 @@
         <v/>
       </c>
       <c r="F49" s="17">
-        <f>IF(B49="","",IF(TRIM(E49)="还不错","种子-数学",IF(TRIM(D49)="完全没有","零基础",IF(TRIM(E49)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B49="","",IF(E49="还不错","种子-数学",IF(D49="完全没有","零基础",IF(E49="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G49" s="22" t="n"/>
@@ -14686,7 +14681,7 @@
         <v/>
       </c>
       <c r="F50" s="17">
-        <f>IF(B50="","",IF(TRIM(E50)="还不错","种子-数学",IF(TRIM(D50)="完全没有","零基础",IF(TRIM(E50)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B50="","",IF(E50="还不错","种子-数学",IF(D50="完全没有","零基础",IF(E50="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G50" s="22" t="n"/>
@@ -14714,7 +14709,7 @@
         <v/>
       </c>
       <c r="F51" s="17">
-        <f>IF(B51="","",IF(TRIM(E51)="还不错","种子-数学",IF(TRIM(D51)="完全没有","零基础",IF(TRIM(E51)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B51="","",IF(E51="还不错","种子-数学",IF(D51="完全没有","零基础",IF(E51="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G51" s="22" t="n"/>
@@ -14742,7 +14737,7 @@
         <v/>
       </c>
       <c r="F52" s="17">
-        <f>IF(B52="","",IF(TRIM(E52)="还不错","种子-数学",IF(TRIM(D52)="完全没有","零基础",IF(TRIM(E52)="看到数字就头大","需帮扶","普通"))))</f>
+        <f>IF(B52="","",IF(E52="还不错","种子-数学",IF(D52="完全没有","零基础",IF(E52="看到数字就头大","需帮扶","普通"))))</f>
         <v/>
       </c>
       <c r="G52" s="22" t="n"/>
@@ -14962,7 +14957,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>

--- a/90_通用工具_全学期复用/90-C4_学生档案汇总表_v2.4_20260820.xlsx
+++ b/90_通用工具_全学期复用/90-C4_学生档案汇总表_v2.4_20260820.xlsx
@@ -322,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -478,6 +478,15 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1011,7 +1020,7 @@
     <row r="19" ht="88" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>问卷还没收回来时，「分组怎么做」左边是空的，F 列标签也是空的，正常。标签不是学期一开始就有的，是贴进「学生档案」之后，按第1题、第2题自动打的。你只在 G 列下拉选出纳组、记账组、成本组、审核组、仓管组、报表组。先把「种子-数学」一人一组、再把「零基础」一人一组、需帮扶跟着种子、剩下的人往人少的组填。不要让学委分组——学委会把熟人放一起，标签就没用了。学委只可以帮你核对宿舍号写得对不对。填完看右边：每组都要有种子、都要有零基础。详细步骤和假人例子写在「分组怎么做」最下面。不要跟学生说「种子」「零基础」。打印 90-C10 桌签放到桌上。出纳组不用专门上一堂课：桌签上已有一行「管钱的」。你说：你们这组叫出纳组，管钱的，库存现金、银行存款以后从你们这过。现在先坐一起。</t>
+          <t>问卷还没收回来时，「分组怎么做」左边是空的，F 列标签也是空的，正常。标签不是学期一开始就有的，是贴进「学生档案」之后，按第1题、第2题自动打的。你只在 G 列下拉选出纳组、记账组、成本组、审核组、仓管组、报表组。先把「种子-数学」一人一组、再把「零基础」一人一组、需帮扶跟着种子、剩下的人往人少的组填。不要让学委分组——学委会把熟人放一起，标签就没用了。学委只可以帮你核对宿舍号写得对不对。填完看右边：每组都要有种子、都要有零基础。详细步骤和假人例子写在「分组怎么做」最下面。不要跟学生说「种子」「零基础」。打印 90-C10 桌签放到桌上。出纳组不用专门上一堂课：桌签上已有一行「管钱的」。你说：你们这组叫出纳组，管钱的，库存现金、银行存款以后从你们这过。现在先坐一起。 桌签平时放抽屉，只在打地鼠、填凭证互审、静默十五分带去摆。不要每节课编组任务，不要按知识点改组名。人数不是6组就合并或拆开，还是岗位名。干脆不分组也行。</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13151,14 +13160,15 @@
     <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="78" customHeight="1">
-      <c r="A1" s="55" t="inlineStr">
-        <is>
-          <t>问卷贴进「学生档案」之后再来。现在左边空着、F 列没有标签，正常——标签是贴完第1题第2题才自动打的，学期一开始没有。
-这张表不会自动分组。你只填 G 列（蓝色下拉）。不要让学委分组，学委会把熟人放一起。学委只帮核对宿舍号。
-填法：先把 F 列「种子-数学」每人分到不同组 → 再把「零基础」每人分到不同组 → 「需帮扶」跟着种子走 → 剩下的人往人少的组填。同宿舍能一起就一起。
-填完看右边：每组「种子」不能是 0，「零基础」不能是 0。上课说一句即可：你们这组叫出纳组，管钱的。不用讲岗位课。桌签 90-C10。
-不要按组布置课后作业。出纳组、记账组不是作业标签。组的任务只出现在课堂上：打地鼠按组上台、填凭证时出纳组先填收付款、审核组审别人的。种子/零基础只给你看，不要跟学生说。</t>
+    <row r="1" ht="96" customHeight="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>问卷贴进「学生档案」之后再来。现在左边空着、F 列没有标签，正常。
+这张表不会自动分组。你只填 G 列。不要让学委分组。
+填法：种子-数学每人不同组 → 零基础每人不同组 → 需帮扶跟着种子 → 剩下的人往人少的组填。
+桌签不是每节课都带。平时放抽屉。只在这三种课带去摆：打地鼠按组上台、填凭证互审、静默十五分讨论。其余课个人写册子、抽 3 人举册子，不摆桌签也正常。
+组名固定用岗位（出纳/记账/成本/审核/仓管/报表），不要按当天知识点改成「资产组」「同增组」。人数不是 6 组时：4 组合并（仓管+报表、成本+审核）；8 组把出纳、记账拆成 A/B。每个项目结束轮换桌签，不是每节课换。
+不要按组布置课后作业。PPT/主文档不要每页加组任务——只在打地鼠、凭证互审那几页写「按组」。</t>
         </is>
       </c>
       <c r="B1" s="46" t="n"/>
@@ -14788,7 +14798,7 @@
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="58" t="inlineStr">
         <is>
-          <t>第 5 步　打印 90-C10 岗位桌签，上课放到对应桌上。跟学生只说：你们这组今天是出纳组。不要说「种子」「零基础」「标签」。</t>
+          <t>第 5 步　打印 90-C10 桌签，塑封后放抽屉。不要每节课都带。只有打地鼠、填凭证互审、静默十五分这三种课，才拿到教室摆桌上。跟学生只说：你们这组是出纳组。不要说种子、零基础。</t>
         </is>
       </c>
     </row>
@@ -14851,7 +14861,7 @@
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="59" t="inlineStr">
         <is>
-          <t>1. 6 个岗位组，桌签每节课放桌上：出纳 / 记账 / 成本 / 审核 / 仓管 / 报表。组名是岗位，不是宿舍号。</t>
+          <t>1. 组名固定是岗位，不是宿舍号，也不是当天的知识点。桌签平时放抽屉，不是每节课都摆。</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14889,7 @@
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="59" t="inlineStr">
         <is>
-          <t>5. 每个项目结束可以轮换桌签，岗位轮一遍。</t>
+          <t>5. 每个项目结束轮换一次桌签（出纳改当审核），不是每节课换，也不是讲到要素就改成资产组。</t>
         </is>
       </c>
     </row>
@@ -14911,13 +14921,50 @@
         </is>
       </c>
     </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="69" t="inlineStr">
+        <is>
+          <t>桌签不是每节课都带；组名不要跟着课文改</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" s="70" t="inlineStr">
+        <is>
+          <t>不要每节课编一道「出纳组专属作业」。举册子、暂停点、加分题全是个人的。为了让桌签显得有用而去编题，你改不动，学生也不按岗位在宿舍做账。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" s="70" t="inlineStr">
+        <is>
+          <t>不要把组名改成六个会计要素、或四种等式变化。有时 4 组、有时 8 组，对不上。要素和等式变化用全班一起写册子就行。岗位名留到项目四填凭证才真正用上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1">
+      <c r="A85" s="70" t="inlineStr">
+        <is>
+          <t>人数不是 6：大约 4 组就合并（仓管+报表、成本+审核）；大约 8 组就拆（出纳A/出纳B）。还是岗位名。宁可少一组，不要为凑数改成「资产组」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="40" customHeight="1">
+      <c r="A86" s="70" t="inlineStr">
+        <is>
+          <t>能不能干脆不分组？能。举册子本来就是个人的。凭证互审改成同桌交换（制单和审核不能同一人）。打地鼠改成抽人上台。桌签可以整学期不拿出来。分组只是让打地鼠和互审省事，不是这门课的必需品。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="31">
     <mergeCell ref="A67:H67"/>
     <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A83:H83"/>
     <mergeCell ref="A59:H59"/>
     <mergeCell ref="A73:H73"/>
     <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A82:H82"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A79:H79"/>
     <mergeCell ref="A61:H61"/>
@@ -14928,13 +14975,16 @@
     <mergeCell ref="A66:H66"/>
     <mergeCell ref="A80:H80"/>
     <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A84:H84"/>
     <mergeCell ref="A74:H74"/>
     <mergeCell ref="J10:M10"/>
     <mergeCell ref="A56:H56"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A86:H86"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A85:H85"/>
     <mergeCell ref="A63:H63"/>
     <mergeCell ref="A72:H72"/>
     <mergeCell ref="A68:H68"/>

--- a/90_通用工具_全学期复用/90-C4_学生档案汇总表_v2.4_20260820.xlsx
+++ b/90_通用工具_全学期复用/90-C4_学生档案汇总表_v2.4_20260820.xlsx
@@ -322,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -486,6 +486,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1013,14 +1025,14 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="52" t="inlineStr">
         <is>
-          <t>这张表不会自动分组。Excel 不会帮你把人分好。你只填 G 列。</t>
+          <t>默认不分组。不要为了摆桌签去编组任务。完整说法见 90-C12，和本表「分组怎么做」最上面几行。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>问卷还没收回来时，「分组怎么做」左边是空的，F 列标签也是空的，正常。标签不是学期一开始就有的，是贴进「学生档案」之后，按第1题、第2题自动打的。你只在 G 列下拉选出纳组、记账组、成本组、审核组、仓管组、报表组。先把「种子-数学」一人一组、再把「零基础」一人一组、需帮扶跟着种子、剩下的人往人少的组填。不要让学委分组——学委会把熟人放一起，标签就没用了。学委只可以帮你核对宿舍号写得对不对。填完看右边：每组都要有种子、都要有零基础。详细步骤和假人例子写在「分组怎么做」最下面。不要跟学生说「种子」「零基础」。打印 90-C10 桌签放到桌上。出纳组不用专门上一堂课：桌签上已有一行「管钱的」。你说：你们这组叫出纳组，管钱的，库存现金、银行存款以后从你们这过。现在先坐一起。 桌签平时放抽屉，只在打地鼠、填凭证互审、静默十五分带去摆。不要每节课编组任务，不要按知识点改组名。人数不是6组就合并或拆开，还是岗位名。干脆不分组也行。</t>
+          <t>真正要用两个人的，只有项目四起「自己填的自己不能审」：同桌交换即可。六个岗位名对不上每节课的活，成本/仓管/报表在项目四常常没事干。打地鼠抽人上台。桌签可以整学期不拿。G 列默认不填。</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13160,15 +13172,13 @@
     <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="96" customHeight="1">
-      <c r="A1" s="68" t="inlineStr">
-        <is>
-          <t>问卷贴进「学生档案」之后再来。现在左边空着、F 列没有标签，正常。
-这张表不会自动分组。你只填 G 列。不要让学委分组。
-填法：种子-数学每人不同组 → 零基础每人不同组 → 需帮扶跟着种子 → 剩下的人往人少的组填。
-桌签不是每节课都带。平时放抽屉。只在这三种课带去摆：打地鼠按组上台、填凭证互审、静默十五分讨论。其余课个人写册子、抽 3 人举册子，不摆桌签也正常。
-组名固定用岗位（出纳/记账/成本/审核/仓管/报表），不要按当天知识点改成「资产组」「同增组」。人数不是 6 组时：4 组合并（仓管+报表、成本+审核）；8 组把出纳、记账拆成 A/B。每个项目结束轮换桌签，不是每节课换。
-不要按组布置课后作业。PPT/主文档不要每页加组任务——只在打地鼠、凭证互审那几页写「按组」。</t>
+    <row r="1" ht="78" customHeight="1">
+      <c r="A1" s="71" t="inlineStr">
+        <is>
+          <t>默认不分组。举册子、暂停点、加分全是个人的，不需要组。
+真正用得上「两个人」的只有一件事：自己填的凭证，自己不能审。这件事从项目四开始，用同桌交换就行，不用六张桌签。
+下面 G 列那套出纳/记账/成本/审核/仓管/报表，是以前设想的岗位组。项目四里成本、仓管、报表往往没事干，变成花架子。默认不要填 G 列、不要每节课摆桌签。
+完整说法见 90-C12《分组到底怎么用》。</t>
         </is>
       </c>
       <c r="B1" s="46" t="n"/>
@@ -14754,241 +14764,177 @@
       <c r="H52" s="15" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="57" t="inlineStr">
-        <is>
-          <t>你具体做什么（贴完学生档案之后）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="36" customHeight="1">
-      <c r="A55" s="58" t="inlineStr">
-        <is>
-          <t>第 0 步　现在先别动。问卷还没收回来，左边空着是正常的。收回来并贴进「学生档案」之后，这张表左边会自动出现全班名单，F 列自动打标签。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="58" t="inlineStr">
-        <is>
-          <t>第 1 步　只看 F 列（紫色，自动的）。四种标签：种子-数学＝第2题选了「还不错」；零基础＝第1题选了「完全没有」；需帮扶＝第2题选了「看到数字就头大」；普通＝其他人。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="36" customHeight="1">
-      <c r="A57" s="58" t="inlineStr">
-        <is>
-          <t>第 2 步　只填 G 列。点蓝色格子，下拉选出纳组 / 记账组 / 成本组 / 审核组 / 仓管组 / 报表组。先筛「种子-数学」，6 个人分别放进 6 个组（一人一组）。</t>
+      <c r="A54" s="69" t="inlineStr">
+        <is>
+          <t>结论（先看这个）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="70" t="inlineStr">
+        <is>
+          <t>分组不是必需品。这门课大部分时间是每个人自己写册子、老师抽三个人看。不分组，课也能上完，而且更省事。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="70" t="inlineStr">
+        <is>
+          <t>以前说的六个岗位组，问题在这里：项目四填凭证时，出纳、记账、审核能对上活；成本、仓管、报表常常没有对应的活。人坐在「报表组」却在填跟别人一样的凭证，组名就是摆设。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="48" customHeight="1">
+      <c r="A57" s="70" t="inlineStr">
+        <is>
+          <t>以前说的「人数不是 6 / 大约 8 组」是这个意思：全班如果不是刚好能分成 6 堆，有的班只能分 4 堆或 8 堆。那是我没说清楚，你不用管这句话。</t>
         </is>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1">
-      <c r="A58" s="58" t="inlineStr">
-        <is>
-          <t>第 3 步　再筛「零基础」，也是 6 个组每个组放 1 个。然后「需帮扶」尽量跟种子同一组（种子能带）。剩下的人往人数少的组填。同宿舍能分一起就一起，不要为了同宿舍把种子拆走。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="36" customHeight="1">
-      <c r="A59" s="58" t="inlineStr">
-        <is>
-          <t>第 4 步　看右边人数表。人数差不要超过 2；「种子」列不能是 0；「零基础」列不能是 0。哪组是 0，把人调一下。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="36" customHeight="1">
-      <c r="A60" s="58" t="inlineStr">
-        <is>
-          <t>第 5 步　打印 90-C10 桌签，塑封后放抽屉。不要每节课都带。只有打地鼠、填凭证互审、静默十五分这三种课，才拿到教室摆桌上。跟学生只说：你们这组是出纳组。不要说种子、零基础。</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="36" customHeight="1">
-      <c r="A61" s="58" t="inlineStr">
-        <is>
-          <t>分组只用在三件事：打地鼠按组上台；填凭证组内互审（制单和审核不能同一人）；静默十五分四人讨论。举册子、点名加分是个人的，不要为了分组而分组。每个项目结束可以把桌签轮换（出纳这周当审核），别让人整个学期都是仓管。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="57" t="inlineStr">
-        <is>
-          <t>举个假人例子（只演示怎么填 G 列，不是你班上的人）</t>
+      <c r="A58" s="59" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="69" t="inlineStr">
+        <is>
+          <t>真正落地的做法（就按这个）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="48" customHeight="1">
+      <c r="A60" s="70" t="inlineStr">
+        <is>
+          <t>1. 平时不分组。学生按原座位坐。举册子、加分题、打地鼠，全是抽到谁是谁。桌签放抽屉，可以整学期不拿出来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="48" customHeight="1">
+      <c r="A61" s="70" t="inlineStr">
+        <is>
+          <t>2. 从项目四开始，只用「同桌」：自己填完一张凭证，和同桌交换，互审。规则就一句——自己填的自己不能审。下一张对调。不用组名，不用桌签。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48" customHeight="1">
+      <c r="A62" s="70" t="inlineStr">
+        <is>
+          <t>3. 打地鼠：抽人上台，不用按组派代表。没抽到的人看、可以喊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
+      <c r="A63" s="70" t="inlineStr">
+        <is>
+          <t>4. 想讨论时：前后桌四人转头说，不用固定组。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="59" t="inlineStr">
-        <is>
-          <t>假设 F 列打出：王磊＝种子-数学，陈静＝种子-数学，刘洋＝零基础，赵敏＝零基础，周杰＝需帮扶，孙丽＝普通（和王磊同宿舍）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="59" t="inlineStr">
-        <is>
-          <t>G 列这样填：王磊 → 出纳组；陈静 → 记账组。（两个种子先拆开）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="59" t="inlineStr">
-        <is>
-          <t>刘洋 → 出纳组（和王磊一组，种子带零基础）；赵敏 → 记账组（和陈静一组）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="59" t="inlineStr">
-        <is>
-          <t>周杰 → 出纳组（需帮扶跟着种子）；孙丽 → 出纳组（同宿舍加分项，不是必须）。</t>
+      <c r="A64" s="59" t="n"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="69" t="inlineStr">
+        <is>
+          <t>可选：项目四拿出一节课做「岗位走一圈」（不是每节课）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="48" customHeight="1">
+      <c r="A66" s="70" t="inlineStr">
+        <is>
+          <t>如果只想让学生体会「会计科里不是一个人包办」，用 90-C10 桌签摆 6 个角，每人轮流坐 8 分钟：出纳只处理收付款、制单填凭证、审核挑别人的错、仓管只看数量、成本只看料工费、报表先空着看别人怎么把数递过来。一节课体验一次就够。之后仍回同桌互审。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="48" customHeight="1">
+      <c r="A67" s="70" t="inlineStr">
+        <is>
+          <t>这一节不代替每个人自己会填凭证。走一圈是认识分工，不是「从今以后你只做出纳」。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="59" t="inlineStr">
-        <is>
-          <t>然后看右边：出纳组人数 4、种子 1、零基础 1；记账组人数 2、种子 1、零基础 1。记账组人少，把后面的「普通」往记账组填即可。这样就算分好了。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="57" t="inlineStr">
-        <is>
-          <t>分组原则（写在这里免得忘）</t>
+      <c r="A68" s="59" t="n"/>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="69" t="inlineStr">
+        <is>
+          <t>G 列还留着干什么</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="48" customHeight="1">
+      <c r="A70" s="70" t="inlineStr">
+        <is>
+          <t>G 列和右边人数表，是给你以后如果仍想分岗位组用的。默认空着。问卷贴进来之后，F 列标签仍会自动出（种子/零基础），那是给你了解班情的，不是分组命令。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1">
-      <c r="A71" s="59" t="inlineStr">
-        <is>
-          <t>1. 组名固定是岗位，不是宿舍号，也不是当天的知识点。桌签平时放抽屉，不是每节课都摆。</t>
-        </is>
-      </c>
+      <c r="A71" s="59" t="n"/>
     </row>
     <row r="72" ht="28" customHeight="1">
-      <c r="A72" s="59" t="inlineStr">
-        <is>
-          <t>2. 每组必须有 1 个「种子-数学」和 1 个「零基础」。整宿舍切组禁止——差的宿舍会整组不会。</t>
-        </is>
-      </c>
+      <c r="A72" s="59" t="n"/>
     </row>
     <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="59" t="inlineStr">
-        <is>
-          <t>3. 同宿舍只是加分项：两人已经在一组且同宿舍，很好；不要为了同宿舍拆开种子。</t>
-        </is>
-      </c>
+      <c r="A73" s="59" t="n"/>
     </row>
     <row r="74" ht="28" customHeight="1">
-      <c r="A74" s="59" t="inlineStr">
-        <is>
-          <t>4. 不是每项活动都分组。举册子、点名加分是个人的。</t>
-        </is>
-      </c>
+      <c r="A74" s="59" t="n"/>
     </row>
     <row r="75" ht="28" customHeight="1">
-      <c r="A75" s="59" t="inlineStr">
-        <is>
-          <t>5. 每个项目结束轮换一次桌签（出纳改当审核），不是每节课换，也不是讲到要素就改成资产组。</t>
-        </is>
-      </c>
-    </row>
+      <c r="A75" s="59" t="n"/>
+    </row>
+    <row r="76"/>
     <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="57" t="inlineStr">
-        <is>
-          <t>标签现在没有，正常；不要让学委分组；出纳组说一句就行</t>
-        </is>
-      </c>
+      <c r="A77" s="72" t="n"/>
     </row>
     <row r="78" ht="40" customHeight="1">
-      <c r="A78" s="58" t="inlineStr">
-        <is>
-          <t>F 列标签从哪来：贴进「学生档案」之后，按第1题（以前接触过会计吗）和第2题（数学怎么样）自动打。学期一开始、问卷还没收回来时，F 列是空的。不是学委评的，也不是你手写的。</t>
-        </is>
-      </c>
+      <c r="A78" s="59" t="n"/>
     </row>
     <row r="79" ht="40" customHeight="1">
-      <c r="A79" s="58" t="inlineStr">
-        <is>
-          <t>不要让学委分组。学委熟的是谁跟谁玩得好，不是谁数学还行、谁零基础。按熟人切，差的会扎堆。学委只可以帮你看宿舍号写得对不对。</t>
-        </is>
-      </c>
+      <c r="A79" s="59" t="n"/>
     </row>
     <row r="80" ht="40" customHeight="1">
-      <c r="A80" s="58" t="inlineStr">
-        <is>
-          <t>出纳组不用专门讲。桌签上已有「管钱的。库存现金、银行存款从这组过。」上课说：你们这组叫出纳组，管钱的，以后填收付款从你们这过。现在先坐一起。记账组、审核组同理，桌签上各有一行。</t>
-        </is>
-      </c>
-    </row>
+      <c r="A80" s="59" t="n"/>
+    </row>
+    <row r="81"/>
     <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="69" t="inlineStr">
-        <is>
-          <t>桌签不是每节课都带；组名不要跟着课文改</t>
-        </is>
-      </c>
+      <c r="A82" s="73" t="n"/>
     </row>
     <row r="83" ht="40" customHeight="1">
-      <c r="A83" s="70" t="inlineStr">
-        <is>
-          <t>不要每节课编一道「出纳组专属作业」。举册子、暂停点、加分题全是个人的。为了让桌签显得有用而去编题，你改不动，学生也不按岗位在宿舍做账。</t>
-        </is>
-      </c>
+      <c r="A83" s="74" t="n"/>
     </row>
     <row r="84" ht="40" customHeight="1">
-      <c r="A84" s="70" t="inlineStr">
-        <is>
-          <t>不要把组名改成六个会计要素、或四种等式变化。有时 4 组、有时 8 组，对不上。要素和等式变化用全班一起写册子就行。岗位名留到项目四填凭证才真正用上。</t>
-        </is>
-      </c>
+      <c r="A84" s="74" t="n"/>
     </row>
     <row r="85" ht="40" customHeight="1">
-      <c r="A85" s="70" t="inlineStr">
-        <is>
-          <t>人数不是 6：大约 4 组就合并（仓管+报表、成本+审核）；大约 8 组就拆（出纳A/出纳B）。还是岗位名。宁可少一组，不要为凑数改成「资产组」。</t>
-        </is>
-      </c>
+      <c r="A85" s="74" t="n"/>
     </row>
     <row r="86" ht="40" customHeight="1">
-      <c r="A86" s="70" t="inlineStr">
-        <is>
-          <t>能不能干脆不分组？能。举册子本来就是个人的。凭证互审改成同桌交换（制单和审核不能同一人）。打地鼠改成抽人上台。桌签可以整学期不拿出来。分组只是让打地鼠和互审省事，不是这门课的必需品。</t>
-        </is>
-      </c>
-    </row>
+      <c r="A86" s="74" t="n"/>
+    </row>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="16">
     <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A77:H77"/>
-    <mergeCell ref="A83:H83"/>
     <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A73:H73"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A82:H82"/>
     <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A79:H79"/>
     <mergeCell ref="A61:H61"/>
     <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A69:H69"/>
     <mergeCell ref="A65:H65"/>
     <mergeCell ref="A54:H54"/>
     <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A84:H84"/>
-    <mergeCell ref="A74:H74"/>
     <mergeCell ref="J10:M10"/>
     <mergeCell ref="A56:H56"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A86:H86"/>
     <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A62:H62"/>
     <mergeCell ref="A63:H63"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="G3:G52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="请用下拉" error="请从下拉列表里选，不要自己改字" type="list">
